--- a/opioid_trends/files for tableau/state_rank_all_years.xlsx
+++ b/opioid_trends/files for tableau/state_rank_all_years.xlsx
@@ -3322,7 +3322,7 @@
         <v>17</v>
       </c>
       <c r="C201" t="n">
-        <v>28.4457542394176</v>
+        <v>28.4620182498461</v>
       </c>
       <c r="D201" t="n">
         <v>18</v>
@@ -3966,7 +3966,7 @@
         <v>31</v>
       </c>
       <c r="C247" t="n">
-        <v>24.5222176201784</v>
+        <v>24.5234307505643</v>
       </c>
       <c r="D247" t="n">
         <v>26</v>
@@ -4005,10 +4005,10 @@
         <v>45627</v>
       </c>
       <c r="B250" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C250" t="n">
-        <v>24.1307790529207</v>
+        <v>24.1380386529147</v>
       </c>
       <c r="D250" t="n">
         <v>27</v>
@@ -4019,10 +4019,10 @@
         <v>45627</v>
       </c>
       <c r="B251" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C251" t="n">
-        <v>24.1286664771613</v>
+        <v>24.1307790529207</v>
       </c>
       <c r="D251" t="n">
         <v>28</v>
@@ -4396,7 +4396,7 @@
         <v>33</v>
       </c>
       <c r="C278" t="n">
-        <v>22.7892523618868</v>
+        <v>22.7942238392781</v>
       </c>
       <c r="D278" t="n">
         <v>32</v>

--- a/opioid_trends/files for tableau/state_rank_all_years.xlsx
+++ b/opioid_trends/files for tableau/state_rank_all_years.xlsx
@@ -80,6 +80,9 @@
     <t xml:space="preserve">Pennsylvania</t>
   </si>
   <si>
+    <t xml:space="preserve">Arizona</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vermont</t>
   </si>
   <si>
@@ -87,9 +90,6 @@
   </si>
   <si>
     <t xml:space="preserve">North Carolina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Arizona</t>
   </si>
   <si>
     <t xml:space="preserve">Florida</t>
@@ -810,83 +810,83 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>44896</v>
+        <v>45992</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="C22" t="n">
-        <v>51.3780052739778</v>
+        <v>51.3793376017706</v>
       </c>
       <c r="D22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>44531</v>
+        <v>44896</v>
       </c>
       <c r="B23" t="s">
+        <v>9</v>
+      </c>
+      <c r="C23" t="n">
+        <v>51.3780052739778</v>
+      </c>
+      <c r="D23" t="n">
         <v>7</v>
-      </c>
-      <c r="C23" t="n">
-        <v>51.1257857279619</v>
-      </c>
-      <c r="D23" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>43070</v>
+        <v>44531</v>
       </c>
       <c r="B24" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C24" t="n">
-        <v>50.9401979641486</v>
+        <v>51.1257857279619</v>
       </c>
       <c r="D24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>44531</v>
+        <v>43070</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C25" t="n">
-        <v>49.3039140670704</v>
+        <v>50.9401979641486</v>
       </c>
       <c r="D25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>43435</v>
+        <v>44531</v>
       </c>
       <c r="B26" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="C26" t="n">
-        <v>48.971460521063</v>
+        <v>49.3039140670704</v>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>42705</v>
+        <v>43435</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27" t="n">
-        <v>48.8048909274539</v>
+        <v>48.971460521063</v>
       </c>
       <c r="D27" t="n">
         <v>1</v>
@@ -894,16 +894,16 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45261</v>
+        <v>42705</v>
       </c>
       <c r="B28" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C28" t="n">
-        <v>48.5086642996613</v>
+        <v>48.8048909274539</v>
       </c>
       <c r="D28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -911,237 +911,237 @@
         <v>45261</v>
       </c>
       <c r="B29" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C29" t="n">
-        <v>48.4185596605762</v>
+        <v>48.5086642996613</v>
       </c>
       <c r="D29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45627</v>
+        <v>45261</v>
       </c>
       <c r="B30" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C30" t="n">
-        <v>48.1492450080706</v>
+        <v>48.4185596605762</v>
       </c>
       <c r="D30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>44896</v>
+        <v>45627</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C31" t="n">
-        <v>47.7394629476345</v>
+        <v>48.1492450080706</v>
       </c>
       <c r="D31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="B32" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C32" t="n">
-        <v>47.4172928708734</v>
+        <v>47.7394629476345</v>
       </c>
       <c r="D32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="B33" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C33" t="n">
-        <v>47.3057645849724</v>
+        <v>47.4172928708734</v>
       </c>
       <c r="D33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45261</v>
+        <v>43800</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C34" t="n">
-        <v>47.1231640217961</v>
+        <v>47.3057645849724</v>
       </c>
       <c r="D34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="B35" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C35" t="n">
-        <v>46.816510652425</v>
+        <v>47.1231640217961</v>
       </c>
       <c r="D35" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45261</v>
+        <v>44166</v>
       </c>
       <c r="B36" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C36" t="n">
-        <v>46.1051880939391</v>
+        <v>46.816510652425</v>
       </c>
       <c r="D36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45627</v>
+        <v>45261</v>
       </c>
       <c r="B37" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C37" t="n">
-        <v>46.0628492929556</v>
+        <v>46.1051880939391</v>
       </c>
       <c r="D37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>44531</v>
+        <v>45627</v>
       </c>
       <c r="B38" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C38" t="n">
-        <v>45.9221355993578</v>
+        <v>46.0628492929556</v>
       </c>
       <c r="D38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45261</v>
+        <v>44531</v>
       </c>
       <c r="B39" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C39" t="n">
-        <v>45.7630298786822</v>
+        <v>45.9221355993578</v>
       </c>
       <c r="D39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="B40" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C40" t="n">
-        <v>45.7280434100695</v>
+        <v>45.7630298786822</v>
       </c>
       <c r="D40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>44531</v>
+        <v>44166</v>
       </c>
       <c r="B41" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C41" t="n">
-        <v>45.687471168995</v>
+        <v>45.7280434100695</v>
       </c>
       <c r="D41" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45627</v>
+        <v>44531</v>
       </c>
       <c r="B42" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C42" t="n">
-        <v>45.4734990552728</v>
+        <v>45.687471168995</v>
       </c>
       <c r="D42" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>44896</v>
+        <v>45627</v>
       </c>
       <c r="B43" t="s">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C43" t="n">
-        <v>45.1278553656173</v>
+        <v>45.4734990552728</v>
       </c>
       <c r="D43" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>44166</v>
+        <v>44896</v>
       </c>
       <c r="B44" t="s">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>45.0470347898687</v>
+        <v>45.1278553656173</v>
       </c>
       <c r="D44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>44166</v>
+        <v>45992</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="C45" t="n">
-        <v>44.9049327930429</v>
+        <v>45.0846368055615</v>
       </c>
       <c r="D45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
@@ -1149,66 +1149,66 @@
         <v>44166</v>
       </c>
       <c r="B46" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C46" t="n">
-        <v>44.30785146173</v>
+        <v>45.0470347898687</v>
       </c>
       <c r="D46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>44531</v>
+        <v>45992</v>
       </c>
       <c r="B47" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C47" t="n">
-        <v>44.303164407189</v>
+        <v>44.9758204010865</v>
       </c>
       <c r="D47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45261</v>
+        <v>44166</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C48" t="n">
-        <v>43.9962473649195</v>
+        <v>44.9049327930429</v>
       </c>
       <c r="D48" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>42705</v>
+        <v>44166</v>
       </c>
       <c r="B49" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C49" t="n">
-        <v>43.9139637621971</v>
+        <v>44.30785146173</v>
       </c>
       <c r="D49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>44896</v>
+        <v>44531</v>
       </c>
       <c r="B50" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C50" t="n">
-        <v>43.7046189681955</v>
+        <v>44.303164407189</v>
       </c>
       <c r="D50" t="n">
         <v>10</v>
@@ -1216,72 +1216,72 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>43070</v>
+        <v>45261</v>
       </c>
       <c r="B51" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C51" t="n">
-        <v>43.6536415743756</v>
+        <v>43.9962473649195</v>
       </c>
       <c r="D51" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45261</v>
+        <v>42705</v>
       </c>
       <c r="B52" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C52" t="n">
-        <v>43.6241660194275</v>
+        <v>43.9139637621971</v>
       </c>
       <c r="D52" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>44531</v>
+        <v>44896</v>
       </c>
       <c r="B53" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C53" t="n">
-        <v>43.3247441981733</v>
+        <v>43.7046189681955</v>
       </c>
       <c r="D53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>43435</v>
+        <v>43070</v>
       </c>
       <c r="B54" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C54" t="n">
-        <v>43.1820643661605</v>
+        <v>43.6536415743756</v>
       </c>
       <c r="D54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="B55" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C55" t="n">
-        <v>43.0800943484619</v>
+        <v>43.6241660194275</v>
       </c>
       <c r="D55" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
@@ -1289,41 +1289,41 @@
         <v>44531</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C56" t="n">
-        <v>42.6470046779787</v>
+        <v>43.3247441981733</v>
       </c>
       <c r="D56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45261</v>
+        <v>43435</v>
       </c>
       <c r="B57" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C57" t="n">
-        <v>42.3910438927461</v>
+        <v>43.1820643661605</v>
       </c>
       <c r="D57" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>44531</v>
+        <v>43800</v>
       </c>
       <c r="B58" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="C58" t="n">
-        <v>42.1265095714177</v>
+        <v>43.0800943484619</v>
       </c>
       <c r="D58" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -1331,97 +1331,97 @@
         <v>44531</v>
       </c>
       <c r="B59" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>41.9716822210144</v>
+        <v>42.6470046779787</v>
       </c>
       <c r="D59" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>43070</v>
+        <v>45261</v>
       </c>
       <c r="B60" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>41.8945850824747</v>
+        <v>42.3910438927461</v>
       </c>
       <c r="D60" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45627</v>
+        <v>44531</v>
       </c>
       <c r="B61" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C61" t="n">
-        <v>41.7861086853667</v>
+        <v>42.1265095714177</v>
       </c>
       <c r="D61" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>44896</v>
+        <v>44531</v>
       </c>
       <c r="B62" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C62" t="n">
-        <v>41.456462142925</v>
+        <v>41.9716822210144</v>
       </c>
       <c r="D62" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>44166</v>
+        <v>45992</v>
       </c>
       <c r="B63" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="C63" t="n">
-        <v>41.4188033637479</v>
+        <v>41.9397494322454</v>
       </c>
       <c r="D63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>44896</v>
+        <v>43070</v>
       </c>
       <c r="B64" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C64" t="n">
-        <v>41.3938746223496</v>
+        <v>41.8945850824747</v>
       </c>
       <c r="D64" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>44531</v>
+        <v>45627</v>
       </c>
       <c r="B65" t="s">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="C65" t="n">
-        <v>41.310317655458</v>
+        <v>41.7861086853667</v>
       </c>
       <c r="D65" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
@@ -1429,27 +1429,27 @@
         <v>44896</v>
       </c>
       <c r="B66" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C66" t="n">
-        <v>41.0436092447764</v>
+        <v>41.456462142925</v>
       </c>
       <c r="D66" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>44896</v>
+        <v>44166</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C67" t="n">
-        <v>41.0340983110638</v>
+        <v>41.4188033637479</v>
       </c>
       <c r="D67" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
@@ -1457,66 +1457,66 @@
         <v>44896</v>
       </c>
       <c r="B68" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C68" t="n">
-        <v>40.9393869631906</v>
+        <v>41.3938746223496</v>
       </c>
       <c r="D68" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>43435</v>
+        <v>44531</v>
       </c>
       <c r="B69" t="s">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="C69" t="n">
-        <v>40.6358336762088</v>
+        <v>41.310317655458</v>
       </c>
       <c r="D69" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="B70" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="C70" t="n">
-        <v>40.5461779982093</v>
+        <v>41.0436092447764</v>
       </c>
       <c r="D70" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>42339</v>
+        <v>44896</v>
       </c>
       <c r="B71" t="s">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="C71" t="n">
-        <v>40.4764112470011</v>
+        <v>41.0340983110638</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="B72" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C72" t="n">
-        <v>40.3146222791772</v>
+        <v>40.9393869631906</v>
       </c>
       <c r="D72" t="n">
         <v>15</v>
@@ -1524,181 +1524,181 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>44896</v>
+        <v>43435</v>
       </c>
       <c r="B73" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="C73" t="n">
-        <v>40.1830286068933</v>
+        <v>40.6358336762088</v>
       </c>
       <c r="D73" t="n">
-        <v>16</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="B74" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="C74" t="n">
-        <v>39.9208983358583</v>
+        <v>40.5461779982093</v>
       </c>
       <c r="D74" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>44896</v>
+        <v>42339</v>
       </c>
       <c r="B75" t="s">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="C75" t="n">
-        <v>39.488457106293</v>
+        <v>40.4764112470011</v>
       </c>
       <c r="D75" t="n">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>44531</v>
+        <v>45261</v>
       </c>
       <c r="B76" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C76" t="n">
-        <v>39.2699573666697</v>
+        <v>40.3146222791772</v>
       </c>
       <c r="D76" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>44531</v>
+        <v>44896</v>
       </c>
       <c r="B77" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C77" t="n">
-        <v>39.1186917213315</v>
+        <v>40.1830286068933</v>
       </c>
       <c r="D77" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>43435</v>
+        <v>45992</v>
       </c>
       <c r="B78" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="C78" t="n">
-        <v>38.919776955361</v>
+        <v>40.0426511438469</v>
       </c>
       <c r="D78" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>44896</v>
+        <v>44166</v>
       </c>
       <c r="B79" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C79" t="n">
-        <v>38.6625443570413</v>
+        <v>39.9208983358583</v>
       </c>
       <c r="D79" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="B80" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C80" t="n">
-        <v>38.422404329979</v>
+        <v>39.488457106293</v>
       </c>
       <c r="D80" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>44166</v>
+        <v>44531</v>
       </c>
       <c r="B81" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C81" t="n">
-        <v>38.4153461680345</v>
+        <v>39.2699573666697</v>
       </c>
       <c r="D81" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>43800</v>
+        <v>44531</v>
       </c>
       <c r="B82" t="s">
+        <v>23</v>
+      </c>
+      <c r="C82" t="n">
+        <v>39.1186917213315</v>
+      </c>
+      <c r="D82" t="n">
         <v>17</v>
-      </c>
-      <c r="C82" t="n">
-        <v>38.383064611221</v>
-      </c>
-      <c r="D82" t="n">
-        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>45261</v>
+        <v>43435</v>
       </c>
       <c r="B83" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C83" t="n">
-        <v>38.3394349141337</v>
+        <v>38.919776955361</v>
       </c>
       <c r="D83" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>44531</v>
+        <v>45992</v>
       </c>
       <c r="B84" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="C84" t="n">
-        <v>38.2525353375544</v>
+        <v>38.7666914696475</v>
       </c>
       <c r="D84" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="B85" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C85" t="n">
-        <v>38.097017351543</v>
+        <v>38.6625443570413</v>
       </c>
       <c r="D85" t="n">
         <v>18</v>
@@ -1706,296 +1706,296 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>44896</v>
+        <v>45261</v>
       </c>
       <c r="B86" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="C86" t="n">
-        <v>37.858352836988</v>
+        <v>38.422404329979</v>
       </c>
       <c r="D86" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>44531</v>
+        <v>44166</v>
       </c>
       <c r="B87" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C87" t="n">
-        <v>37.6192893195365</v>
+        <v>38.4153461680345</v>
       </c>
       <c r="D87" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>44166</v>
+        <v>43800</v>
       </c>
       <c r="B88" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C88" t="n">
-        <v>37.5468268664613</v>
+        <v>38.383064611221</v>
       </c>
       <c r="D88" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="B89" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C89" t="n">
-        <v>37.3488371501707</v>
+        <v>38.3394349141337</v>
       </c>
       <c r="D89" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>45627</v>
+        <v>44531</v>
       </c>
       <c r="B90" t="s">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="C90" t="n">
-        <v>37.2476290900047</v>
+        <v>38.2525353375544</v>
       </c>
       <c r="D90" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>45627</v>
+        <v>45261</v>
       </c>
       <c r="B91" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C91" t="n">
-        <v>37.1675659890223</v>
+        <v>38.097017351543</v>
       </c>
       <c r="D91" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>43070</v>
+        <v>44896</v>
       </c>
       <c r="B92" t="s">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="C92" t="n">
-        <v>37.1469998186563</v>
+        <v>37.858352836988</v>
       </c>
       <c r="D92" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>44896</v>
+        <v>44531</v>
       </c>
       <c r="B93" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C93" t="n">
-        <v>36.9919776987203</v>
+        <v>37.6192893195365</v>
       </c>
       <c r="D93" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>45261</v>
+        <v>44166</v>
       </c>
       <c r="B94" t="s">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="C94" t="n">
-        <v>36.889827006127</v>
+        <v>37.5468268664613</v>
       </c>
       <c r="D94" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>44896</v>
+        <v>44166</v>
       </c>
       <c r="B95" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="C95" t="n">
-        <v>36.8392390523392</v>
+        <v>37.3488371501707</v>
       </c>
       <c r="D95" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>42705</v>
+        <v>45627</v>
       </c>
       <c r="B96" t="s">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="C96" t="n">
-        <v>36.7547009440928</v>
+        <v>37.2476290900047</v>
       </c>
       <c r="D96" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>45261</v>
+        <v>45627</v>
       </c>
       <c r="B97" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="C97" t="n">
-        <v>36.5903019509431</v>
+        <v>37.1675659890223</v>
       </c>
       <c r="D97" t="n">
-        <v>20</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>44531</v>
+        <v>43070</v>
       </c>
       <c r="B98" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="C98" t="n">
-        <v>36.5425355113352</v>
+        <v>37.1469998186563</v>
       </c>
       <c r="D98" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>44166</v>
+        <v>44896</v>
       </c>
       <c r="B99" t="s">
+        <v>26</v>
+      </c>
+      <c r="C99" t="n">
+        <v>36.9919776987203</v>
+      </c>
+      <c r="D99" t="n">
         <v>20</v>
-      </c>
-      <c r="C99" t="n">
-        <v>36.3570093475062</v>
-      </c>
-      <c r="D99" t="n">
-        <v>13</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="B100" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C100" t="n">
-        <v>36.3553780258376</v>
+        <v>36.889827006127</v>
       </c>
       <c r="D100" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>45627</v>
+        <v>44896</v>
       </c>
       <c r="B101" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C101" t="n">
-        <v>36.3426592225618</v>
+        <v>36.8392390523392</v>
       </c>
       <c r="D101" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>44896</v>
+        <v>42705</v>
       </c>
       <c r="B102" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C102" t="n">
-        <v>36.1411112820656</v>
+        <v>36.7547009440928</v>
       </c>
       <c r="D102" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="B103" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C103" t="n">
-        <v>36.1078401174315</v>
+        <v>36.5903019509431</v>
       </c>
       <c r="D103" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>44896</v>
+        <v>44531</v>
       </c>
       <c r="B104" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C104" t="n">
-        <v>36.0170602328343</v>
+        <v>36.5425355113352</v>
       </c>
       <c r="D104" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>42705</v>
+        <v>44166</v>
       </c>
       <c r="B105" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C105" t="n">
-        <v>35.834749993254</v>
+        <v>36.3570093475062</v>
       </c>
       <c r="D105" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>45627</v>
+        <v>43800</v>
       </c>
       <c r="B106" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="C106" t="n">
-        <v>35.7526122644032</v>
+        <v>36.3553780258376</v>
       </c>
       <c r="D106" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107">
@@ -2003,27 +2003,27 @@
         <v>45627</v>
       </c>
       <c r="B107" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C107" t="n">
-        <v>35.7473123317025</v>
+        <v>36.3426592225618</v>
       </c>
       <c r="D107" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>44531</v>
+        <v>44896</v>
       </c>
       <c r="B108" t="s">
-        <v>28</v>
+        <v>14</v>
       </c>
       <c r="C108" t="n">
-        <v>35.740256424535</v>
+        <v>36.1411112820656</v>
       </c>
       <c r="D108" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="109">
@@ -2031,13 +2031,13 @@
         <v>44166</v>
       </c>
       <c r="B109" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="C109" t="n">
-        <v>35.4643130509141</v>
+        <v>36.1078401174315</v>
       </c>
       <c r="D109" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="110">
@@ -2045,111 +2045,111 @@
         <v>44896</v>
       </c>
       <c r="B110" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C110" t="n">
-        <v>35.2724688906298</v>
+        <v>36.0170602328343</v>
       </c>
       <c r="D110" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>45627</v>
+        <v>42705</v>
       </c>
       <c r="B111" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C111" t="n">
-        <v>35.2235664819026</v>
+        <v>35.834749993254</v>
       </c>
       <c r="D111" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>43070</v>
+        <v>45627</v>
       </c>
       <c r="B112" t="s">
+        <v>22</v>
+      </c>
+      <c r="C112" t="n">
+        <v>35.7526122644032</v>
+      </c>
+      <c r="D112" t="n">
         <v>9</v>
-      </c>
-      <c r="C112" t="n">
-        <v>34.8453686700083</v>
-      </c>
-      <c r="D112" t="n">
-        <v>6</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>43070</v>
+        <v>45627</v>
       </c>
       <c r="B113" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C113" t="n">
-        <v>34.835206879589</v>
+        <v>35.7473123317025</v>
       </c>
       <c r="D113" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>43070</v>
+        <v>44531</v>
       </c>
       <c r="B114" t="s">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="C114" t="n">
-        <v>34.7288703849303</v>
+        <v>35.740256424535</v>
       </c>
       <c r="D114" t="n">
-        <v>8</v>
+        <v>21</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>44531</v>
+        <v>44166</v>
       </c>
       <c r="B115" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="C115" t="n">
-        <v>34.6490459283295</v>
+        <v>35.4643130509141</v>
       </c>
       <c r="D115" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>45261</v>
+        <v>45992</v>
       </c>
       <c r="B116" t="s">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="C116" t="n">
-        <v>34.3490241362579</v>
+        <v>35.3682770429899</v>
       </c>
       <c r="D116" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>43800</v>
+        <v>44896</v>
       </c>
       <c r="B117" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C117" t="n">
-        <v>34.2619683670441</v>
+        <v>35.2724688906298</v>
       </c>
       <c r="D117" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
     </row>
     <row r="118">
@@ -2157,262 +2157,262 @@
         <v>45627</v>
       </c>
       <c r="B118" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C118" t="n">
-        <v>34.2223352582841</v>
+        <v>35.2235664819026</v>
       </c>
       <c r="D118" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>43800</v>
+        <v>43070</v>
       </c>
       <c r="B119" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="C119" t="n">
-        <v>34.1438925146935</v>
+        <v>34.8453686700083</v>
       </c>
       <c r="D119" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>44166</v>
+        <v>43070</v>
       </c>
       <c r="B120" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="C120" t="n">
-        <v>34.0427844359304</v>
+        <v>34.835206879589</v>
       </c>
       <c r="D120" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>45261</v>
+        <v>43070</v>
       </c>
       <c r="B121" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C121" t="n">
-        <v>34.0396221201479</v>
+        <v>34.7288703849303</v>
       </c>
       <c r="D121" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>43435</v>
+        <v>44531</v>
       </c>
       <c r="B122" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C122" t="n">
-        <v>34.0383866652789</v>
+        <v>34.6490459283295</v>
       </c>
       <c r="D122" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>43435</v>
+        <v>45261</v>
       </c>
       <c r="B123" t="s">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="C123" t="n">
-        <v>34.018914142429</v>
+        <v>34.3490241362579</v>
       </c>
       <c r="D123" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>44531</v>
+        <v>43800</v>
       </c>
       <c r="B124" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C124" t="n">
-        <v>33.9627057456792</v>
+        <v>34.2619683670441</v>
       </c>
       <c r="D124" t="n">
-        <v>23</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>42705</v>
+        <v>45627</v>
       </c>
       <c r="B125" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="C125" t="n">
-        <v>33.7315576286748</v>
+        <v>34.2223352582841</v>
       </c>
       <c r="D125" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>45261</v>
+        <v>43800</v>
       </c>
       <c r="B126" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C126" t="n">
-        <v>33.6547949835546</v>
+        <v>34.1438925146935</v>
       </c>
       <c r="D126" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>45261</v>
+        <v>44166</v>
       </c>
       <c r="B127" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="C127" t="n">
-        <v>33.6526432176819</v>
+        <v>34.0427844359304</v>
       </c>
       <c r="D127" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="B128" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="C128" t="n">
-        <v>33.5785192272941</v>
+        <v>34.0396221201479</v>
       </c>
       <c r="D128" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>44896</v>
+        <v>43435</v>
       </c>
       <c r="B129" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C129" t="n">
-        <v>33.5620170364603</v>
+        <v>34.0383866652789</v>
       </c>
       <c r="D129" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>44531</v>
+        <v>43435</v>
       </c>
       <c r="B130" t="s">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="C130" t="n">
-        <v>33.4953878755432</v>
+        <v>34.018914142429</v>
       </c>
       <c r="D130" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>42705</v>
+        <v>44531</v>
       </c>
       <c r="B131" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="C131" t="n">
-        <v>33.3776668427861</v>
+        <v>33.9627057456792</v>
       </c>
       <c r="D131" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>44896</v>
+        <v>42705</v>
       </c>
       <c r="B132" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="C132" t="n">
-        <v>33.1830587275722</v>
+        <v>33.7315576286748</v>
       </c>
       <c r="D132" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>44896</v>
+        <v>45261</v>
       </c>
       <c r="B133" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="C133" t="n">
-        <v>32.9674743895966</v>
+        <v>33.6547949835546</v>
       </c>
       <c r="D133" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="B134" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C134" t="n">
-        <v>32.8382236923779</v>
+        <v>33.6526432176819</v>
       </c>
       <c r="D134" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>45261</v>
+        <v>44166</v>
       </c>
       <c r="B135" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C135" t="n">
-        <v>32.7931099949947</v>
+        <v>33.5785192272941</v>
       </c>
       <c r="D135" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>44531</v>
+        <v>44896</v>
       </c>
       <c r="B136" t="s">
-        <v>31</v>
+        <v>12</v>
       </c>
       <c r="C136" t="n">
-        <v>32.6250187500674</v>
+        <v>33.5620170364603</v>
       </c>
       <c r="D136" t="n">
         <v>25</v>
@@ -2423,52 +2423,52 @@
         <v>44531</v>
       </c>
       <c r="B137" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C137" t="n">
-        <v>32.5860101728131</v>
+        <v>33.4953878755432</v>
       </c>
       <c r="D137" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>44896</v>
+        <v>42705</v>
       </c>
       <c r="B138" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C138" t="n">
-        <v>32.5283765715151</v>
+        <v>33.3776668427861</v>
       </c>
       <c r="D138" t="n">
-        <v>28</v>
+        <v>6</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>43435</v>
+        <v>45992</v>
       </c>
       <c r="B139" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="C139" t="n">
-        <v>32.5031428207044</v>
+        <v>33.3030516594493</v>
       </c>
       <c r="D139" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="B140" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="C140" t="n">
-        <v>32.4824405229184</v>
+        <v>33.1830587275722</v>
       </c>
       <c r="D140" t="n">
         <v>26</v>
@@ -2479,27 +2479,27 @@
         <v>44896</v>
       </c>
       <c r="B141" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="C141" t="n">
-        <v>32.4295461121587</v>
+        <v>32.9674743895966</v>
       </c>
       <c r="D141" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>45261</v>
+        <v>44166</v>
       </c>
       <c r="B142" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="C142" t="n">
-        <v>32.4151471933102</v>
+        <v>32.8382236923779</v>
       </c>
       <c r="D142" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
     </row>
     <row r="143">
@@ -2507,83 +2507,83 @@
         <v>45261</v>
       </c>
       <c r="B143" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C143" t="n">
-        <v>32.409061114123</v>
+        <v>32.7931099949947</v>
       </c>
       <c r="D143" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>45627</v>
+        <v>44531</v>
       </c>
       <c r="B144" t="s">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="C144" t="n">
-        <v>32.2718825586901</v>
+        <v>32.6250187500674</v>
       </c>
       <c r="D144" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>43435</v>
+        <v>44531</v>
       </c>
       <c r="B145" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="C145" t="n">
-        <v>32.0086866827273</v>
+        <v>32.5860101728131</v>
       </c>
       <c r="D145" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>42705</v>
+        <v>44896</v>
       </c>
       <c r="B146" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="C146" t="n">
-        <v>31.9749647374215</v>
+        <v>32.5283765715151</v>
       </c>
       <c r="D146" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>45261</v>
+        <v>43435</v>
       </c>
       <c r="B147" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="C147" t="n">
-        <v>31.9748683137659</v>
+        <v>32.5031428207044</v>
       </c>
       <c r="D147" t="n">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>45627</v>
+        <v>45261</v>
       </c>
       <c r="B148" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C148" t="n">
-        <v>31.9495290951114</v>
+        <v>32.4824405229184</v>
       </c>
       <c r="D148" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
     </row>
     <row r="149">
@@ -2591,13 +2591,13 @@
         <v>44896</v>
       </c>
       <c r="B149" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C149" t="n">
-        <v>31.8929212226436</v>
+        <v>32.4295461121587</v>
       </c>
       <c r="D149" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="150">
@@ -2605,55 +2605,55 @@
         <v>45261</v>
       </c>
       <c r="B150" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C150" t="n">
-        <v>31.8631374400477</v>
+        <v>32.4151471933102</v>
       </c>
       <c r="D150" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>42705</v>
+        <v>45261</v>
       </c>
       <c r="B151" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="C151" t="n">
-        <v>31.6864615471968</v>
+        <v>32.409061114123</v>
       </c>
       <c r="D151" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="B152" t="s">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="C152" t="n">
-        <v>31.6797323513141</v>
+        <v>32.2718825586901</v>
       </c>
       <c r="D152" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>44531</v>
+        <v>43435</v>
       </c>
       <c r="B153" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C153" t="n">
-        <v>31.5557417967825</v>
+        <v>32.0086866827273</v>
       </c>
       <c r="D153" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="154">
@@ -2661,13 +2661,13 @@
         <v>42705</v>
       </c>
       <c r="B154" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C154" t="n">
-        <v>31.436592193313</v>
+        <v>31.9749647374215</v>
       </c>
       <c r="D154" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="155">
@@ -2675,94 +2675,94 @@
         <v>45261</v>
       </c>
       <c r="B155" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="C155" t="n">
-        <v>31.3493583494235</v>
+        <v>31.9748683137659</v>
       </c>
       <c r="D155" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>45261</v>
+        <v>45627</v>
       </c>
       <c r="B156" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C156" t="n">
-        <v>31.337110791262</v>
+        <v>31.9495290951114</v>
       </c>
       <c r="D156" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>44166</v>
+        <v>44896</v>
       </c>
       <c r="B157" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C157" t="n">
-        <v>31.1811348760749</v>
+        <v>31.8929212226436</v>
       </c>
       <c r="D157" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="B158" t="s">
-        <v>6</v>
+        <v>35</v>
       </c>
       <c r="C158" t="n">
-        <v>31.1684661426341</v>
+        <v>31.8631374400477</v>
       </c>
       <c r="D158" t="n">
-        <v>9</v>
+        <v>30</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>43435</v>
+        <v>42705</v>
       </c>
       <c r="B159" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C159" t="n">
-        <v>30.9399239161605</v>
+        <v>31.6864615471968</v>
       </c>
       <c r="D159" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>44531</v>
+        <v>43800</v>
       </c>
       <c r="B160" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C160" t="n">
-        <v>30.7279136660905</v>
+        <v>31.6797323513141</v>
       </c>
       <c r="D160" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>43070</v>
+        <v>45992</v>
       </c>
       <c r="B161" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="C161" t="n">
-        <v>30.5784504591916</v>
+        <v>31.6782150330516</v>
       </c>
       <c r="D161" t="n">
         <v>9</v>
@@ -2770,97 +2770,97 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>44166</v>
+        <v>44531</v>
       </c>
       <c r="B162" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C162" t="n">
-        <v>30.5067433223046</v>
+        <v>31.5557417967825</v>
       </c>
       <c r="D162" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>45627</v>
+        <v>42705</v>
       </c>
       <c r="B163" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="C163" t="n">
-        <v>30.4959297549611</v>
+        <v>31.436592193313</v>
       </c>
       <c r="D163" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="B164" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="C164" t="n">
-        <v>30.4618835946625</v>
+        <v>31.3493583494235</v>
       </c>
       <c r="D164" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>43070</v>
+        <v>45261</v>
       </c>
       <c r="B165" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="C165" t="n">
-        <v>30.4043503863276</v>
+        <v>31.337110791262</v>
       </c>
       <c r="D165" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>44531</v>
+        <v>44166</v>
       </c>
       <c r="B166" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C166" t="n">
-        <v>30.3292323814599</v>
+        <v>31.1811348760749</v>
       </c>
       <c r="D166" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>44896</v>
+        <v>43800</v>
       </c>
       <c r="B167" t="s">
-        <v>39</v>
+        <v>6</v>
       </c>
       <c r="C167" t="n">
-        <v>30.3151016381906</v>
+        <v>31.1684661426341</v>
       </c>
       <c r="D167" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>43435</v>
+        <v>45992</v>
       </c>
       <c r="B168" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C168" t="n">
-        <v>30.3127710176941</v>
+        <v>31.0372611869354</v>
       </c>
       <c r="D168" t="n">
         <v>10</v>
@@ -2868,44 +2868,44 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B169" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="C169" t="n">
-        <v>30.2439557636599</v>
+        <v>30.9399239161605</v>
       </c>
       <c r="D169" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>43070</v>
+        <v>44531</v>
       </c>
       <c r="B170" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C170" t="n">
-        <v>30.1389930776112</v>
+        <v>30.7279136660905</v>
       </c>
       <c r="D170" t="n">
-        <v>11</v>
+        <v>28</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>44896</v>
+        <v>43070</v>
       </c>
       <c r="B171" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C171" t="n">
-        <v>30.1283445640644</v>
+        <v>30.5784504591916</v>
       </c>
       <c r="D171" t="n">
-        <v>32</v>
+        <v>9</v>
       </c>
     </row>
     <row r="172">
@@ -2913,178 +2913,178 @@
         <v>44166</v>
       </c>
       <c r="B172" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C172" t="n">
-        <v>30.1050774272496</v>
+        <v>30.5067433223046</v>
       </c>
       <c r="D172" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="B173" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="C173" t="n">
-        <v>30.0410741839094</v>
+        <v>30.4959297549611</v>
       </c>
       <c r="D173" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>44896</v>
+        <v>43800</v>
       </c>
       <c r="B174" t="s">
-        <v>35</v>
+        <v>9</v>
       </c>
       <c r="C174" t="n">
-        <v>29.963506829552</v>
+        <v>30.4618835946625</v>
       </c>
       <c r="D174" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>44531</v>
+        <v>43070</v>
       </c>
       <c r="B175" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="C175" t="n">
-        <v>29.9574515626839</v>
+        <v>30.4043503863276</v>
       </c>
       <c r="D175" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>43070</v>
+        <v>44531</v>
       </c>
       <c r="B176" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C176" t="n">
-        <v>29.9556489974565</v>
+        <v>30.3292323814599</v>
       </c>
       <c r="D176" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>44166</v>
+        <v>44896</v>
       </c>
       <c r="B177" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C177" t="n">
-        <v>29.9094088135673</v>
+        <v>30.3151016381906</v>
       </c>
       <c r="D177" t="n">
-        <v>22</v>
+        <v>31</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>44896</v>
+        <v>43435</v>
       </c>
       <c r="B178" t="s">
-        <v>36</v>
+        <v>20</v>
       </c>
       <c r="C178" t="n">
-        <v>29.8083760649664</v>
+        <v>30.3127710176941</v>
       </c>
       <c r="D178" t="n">
-        <v>34</v>
+        <v>10</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>43435</v>
+        <v>42339</v>
       </c>
       <c r="B179" t="s">
-        <v>9</v>
+        <v>29</v>
       </c>
       <c r="C179" t="n">
-        <v>29.7275942165588</v>
+        <v>30.2439557636599</v>
       </c>
       <c r="D179" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>44531</v>
+        <v>43070</v>
       </c>
       <c r="B180" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C180" t="n">
-        <v>29.7215677234277</v>
+        <v>30.1389930776112</v>
       </c>
       <c r="D180" t="n">
-        <v>31</v>
+        <v>11</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="B181" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C181" t="n">
-        <v>29.7019872230362</v>
+        <v>30.1283445640644</v>
       </c>
       <c r="D181" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>43435</v>
+        <v>44166</v>
       </c>
       <c r="B182" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="C182" t="n">
-        <v>29.6782818771097</v>
+        <v>30.1050774272496</v>
       </c>
       <c r="D182" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>44531</v>
+        <v>43800</v>
       </c>
       <c r="B183" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C183" t="n">
-        <v>29.5554330914958</v>
+        <v>30.0410741839094</v>
       </c>
       <c r="D183" t="n">
-        <v>32</v>
+        <v>11</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>44531</v>
+        <v>44896</v>
       </c>
       <c r="B184" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="C184" t="n">
-        <v>29.5278054671364</v>
+        <v>29.963506829552</v>
       </c>
       <c r="D184" t="n">
         <v>33</v>
@@ -3092,44 +3092,44 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>44896</v>
+        <v>44531</v>
       </c>
       <c r="B185" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C185" t="n">
-        <v>29.5055548753631</v>
+        <v>29.9574515626839</v>
       </c>
       <c r="D185" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>42339</v>
+        <v>43070</v>
       </c>
       <c r="B186" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C186" t="n">
-        <v>29.2138185940918</v>
+        <v>29.9556489974565</v>
       </c>
       <c r="D186" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>45627</v>
+        <v>44166</v>
       </c>
       <c r="B187" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C187" t="n">
-        <v>29.1204616429965</v>
+        <v>29.9094088135673</v>
       </c>
       <c r="D187" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="188">
@@ -3137,69 +3137,69 @@
         <v>44896</v>
       </c>
       <c r="B188" t="s">
+        <v>36</v>
+      </c>
+      <c r="C188" t="n">
+        <v>29.8083760649664</v>
+      </c>
+      <c r="D188" t="n">
         <v>34</v>
-      </c>
-      <c r="C188" t="n">
-        <v>29.0535098820952</v>
-      </c>
-      <c r="D188" t="n">
-        <v>36</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>43800</v>
+        <v>43435</v>
       </c>
       <c r="B189" t="s">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="C189" t="n">
-        <v>29.0306598568248</v>
+        <v>29.7275942165588</v>
       </c>
       <c r="D189" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>42705</v>
+        <v>44531</v>
       </c>
       <c r="B190" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C190" t="n">
-        <v>29.0255954830063</v>
+        <v>29.7215677234277</v>
       </c>
       <c r="D190" t="n">
-        <v>10</v>
+        <v>31</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>44896</v>
+        <v>45261</v>
       </c>
       <c r="B191" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C191" t="n">
-        <v>29.02424812225</v>
+        <v>29.7019872230362</v>
       </c>
       <c r="D191" t="n">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>44166</v>
+        <v>43435</v>
       </c>
       <c r="B192" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="C192" t="n">
-        <v>28.9883532277596</v>
+        <v>29.6782818771097</v>
       </c>
       <c r="D192" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
     </row>
     <row r="193">
@@ -3207,181 +3207,181 @@
         <v>44531</v>
       </c>
       <c r="B193" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C193" t="n">
-        <v>28.8883488128975</v>
+        <v>29.5554330914958</v>
       </c>
       <c r="D193" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>45261</v>
+        <v>44531</v>
       </c>
       <c r="B194" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C194" t="n">
-        <v>28.8823160953448</v>
+        <v>29.5278054671364</v>
       </c>
       <c r="D194" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>43800</v>
+        <v>44896</v>
       </c>
       <c r="B195" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="C195" t="n">
-        <v>28.8712342950441</v>
+        <v>29.5055548753631</v>
       </c>
       <c r="D195" t="n">
-        <v>13</v>
+        <v>35</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>43800</v>
+        <v>42339</v>
       </c>
       <c r="B196" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C196" t="n">
-        <v>28.786415726857</v>
+        <v>29.2138185940918</v>
       </c>
       <c r="D196" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>45261</v>
+        <v>45627</v>
       </c>
       <c r="B197" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>28.6707732621834</v>
+        <v>29.1204616429965</v>
       </c>
       <c r="D197" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>45627</v>
+        <v>44896</v>
       </c>
       <c r="B198" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C198" t="n">
-        <v>28.6554179008299</v>
+        <v>29.0535098820952</v>
       </c>
       <c r="D198" t="n">
-        <v>17</v>
+        <v>36</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>44166</v>
+        <v>43800</v>
       </c>
       <c r="B199" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C199" t="n">
-        <v>28.6406617231767</v>
+        <v>29.0306598568248</v>
       </c>
       <c r="D199" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>45261</v>
+        <v>42705</v>
       </c>
       <c r="B200" t="s">
-        <v>38</v>
+        <v>7</v>
       </c>
       <c r="C200" t="n">
-        <v>28.5698339605608</v>
+        <v>29.0255954830063</v>
       </c>
       <c r="D200" t="n">
-        <v>36</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>45627</v>
+        <v>44896</v>
       </c>
       <c r="B201" t="s">
-        <v>17</v>
+        <v>38</v>
       </c>
       <c r="C201" t="n">
-        <v>28.4457542394176</v>
+        <v>29.02424812225</v>
       </c>
       <c r="D201" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>43070</v>
+        <v>44166</v>
       </c>
       <c r="B202" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="C202" t="n">
-        <v>28.3841584124105</v>
+        <v>28.9883532277596</v>
       </c>
       <c r="D202" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>42339</v>
+        <v>44531</v>
       </c>
       <c r="B203" t="s">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="C203" t="n">
-        <v>28.3434309638219</v>
+        <v>28.8883488128975</v>
       </c>
       <c r="D203" t="n">
-        <v>4</v>
+        <v>34</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>44531</v>
+        <v>45261</v>
       </c>
       <c r="B204" t="s">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="C204" t="n">
-        <v>28.0710794910697</v>
+        <v>28.8823160953448</v>
       </c>
       <c r="D204" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>44166</v>
+        <v>43800</v>
       </c>
       <c r="B205" t="s">
-        <v>31</v>
+        <v>11</v>
       </c>
       <c r="C205" t="n">
-        <v>28.0469679563528</v>
+        <v>28.8712342950441</v>
       </c>
       <c r="D205" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="206">
@@ -3389,55 +3389,55 @@
         <v>43800</v>
       </c>
       <c r="B206" t="s">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C206" t="n">
-        <v>27.9990251873133</v>
+        <v>28.786415726857</v>
       </c>
       <c r="D206" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="B207" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="C207" t="n">
-        <v>27.9833760947384</v>
+        <v>28.6707732621834</v>
       </c>
       <c r="D207" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>42339</v>
+        <v>45627</v>
       </c>
       <c r="B208" t="s">
-        <v>9</v>
+        <v>30</v>
       </c>
       <c r="C208" t="n">
-        <v>27.7694892082825</v>
+        <v>28.6554179008299</v>
       </c>
       <c r="D208" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>45627</v>
+        <v>44166</v>
       </c>
       <c r="B209" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="C209" t="n">
-        <v>27.6812386106126</v>
+        <v>28.6406617231767</v>
       </c>
       <c r="D209" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="210">
@@ -3445,167 +3445,167 @@
         <v>45261</v>
       </c>
       <c r="B210" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C210" t="n">
-        <v>27.585802413434</v>
+        <v>28.5698339605608</v>
       </c>
       <c r="D210" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>44166</v>
+        <v>45627</v>
       </c>
       <c r="B211" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="C211" t="n">
-        <v>27.539007159128</v>
+        <v>28.4620182498461</v>
       </c>
       <c r="D211" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>44166</v>
+        <v>43070</v>
       </c>
       <c r="B212" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C212" t="n">
-        <v>27.3291599552875</v>
+        <v>28.3841584124105</v>
       </c>
       <c r="D212" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>43070</v>
+        <v>42339</v>
       </c>
       <c r="B213" t="s">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="C213" t="n">
-        <v>27.1797894936413</v>
+        <v>28.3434309638219</v>
       </c>
       <c r="D213" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>42705</v>
+        <v>44531</v>
       </c>
       <c r="B214" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C214" t="n">
-        <v>27.0155575217803</v>
+        <v>28.0710794910697</v>
       </c>
       <c r="D214" t="n">
-        <v>11</v>
+        <v>35</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>43435</v>
+        <v>44166</v>
       </c>
       <c r="B215" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C215" t="n">
-        <v>26.7803892909349</v>
+        <v>28.0469679563528</v>
       </c>
       <c r="D215" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>45627</v>
+        <v>43800</v>
       </c>
       <c r="B216" t="s">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C216" t="n">
-        <v>26.7289873601117</v>
+        <v>27.9990251873133</v>
       </c>
       <c r="D216" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>45627</v>
+        <v>43800</v>
       </c>
       <c r="B217" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C217" t="n">
-        <v>26.7121543615876</v>
+        <v>27.9833760947384</v>
       </c>
       <c r="D217" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>43800</v>
+        <v>42339</v>
       </c>
       <c r="B218" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C218" t="n">
-        <v>26.6755880051229</v>
+        <v>27.7694892082825</v>
       </c>
       <c r="D218" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>44531</v>
+        <v>45627</v>
       </c>
       <c r="B219" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
       <c r="C219" t="n">
-        <v>26.6724026672403</v>
+        <v>27.6812386106126</v>
       </c>
       <c r="D219" t="n">
-        <v>36</v>
+        <v>19</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>43435</v>
+        <v>45261</v>
       </c>
       <c r="B220" t="s">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="C220" t="n">
-        <v>26.6220133276149</v>
+        <v>27.585802413434</v>
       </c>
       <c r="D220" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>43070</v>
+        <v>45992</v>
       </c>
       <c r="B221" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="C221" t="n">
-        <v>26.4844404657604</v>
+        <v>27.5598616406518</v>
       </c>
       <c r="D221" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="222">
@@ -3613,69 +3613,69 @@
         <v>44166</v>
       </c>
       <c r="B222" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C222" t="n">
-        <v>26.4188974793017</v>
+        <v>27.539007159128</v>
       </c>
       <c r="D222" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>42705</v>
+        <v>44166</v>
       </c>
       <c r="B223" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C223" t="n">
-        <v>26.3071406569858</v>
+        <v>27.3291599552875</v>
       </c>
       <c r="D223" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>43800</v>
+        <v>43070</v>
       </c>
       <c r="B224" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C224" t="n">
-        <v>26.1009708649337</v>
+        <v>27.1797894936413</v>
       </c>
       <c r="D224" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>44166</v>
+        <v>42705</v>
       </c>
       <c r="B225" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C225" t="n">
-        <v>26.0743936000392</v>
+        <v>27.0155575217803</v>
       </c>
       <c r="D225" t="n">
-        <v>29</v>
+        <v>11</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>43070</v>
+        <v>43435</v>
       </c>
       <c r="B226" t="s">
         <v>6</v>
       </c>
       <c r="C226" t="n">
-        <v>25.993159556743</v>
+        <v>26.7803892909349</v>
       </c>
       <c r="D226" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="227">
@@ -3683,55 +3683,55 @@
         <v>45627</v>
       </c>
       <c r="B227" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C227" t="n">
-        <v>25.9046385493402</v>
+        <v>26.7289873601117</v>
       </c>
       <c r="D227" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="B228" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="C228" t="n">
-        <v>25.8859494309262</v>
+        <v>26.7121543615876</v>
       </c>
       <c r="D228" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>45627</v>
+        <v>43800</v>
       </c>
       <c r="B229" t="s">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="C229" t="n">
-        <v>25.7589910783215</v>
+        <v>26.6755880051229</v>
       </c>
       <c r="D229" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>44896</v>
+        <v>44531</v>
       </c>
       <c r="B230" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="C230" t="n">
-        <v>25.7494716242528</v>
+        <v>26.6724026672403</v>
       </c>
       <c r="D230" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="231">
@@ -3739,13 +3739,13 @@
         <v>43435</v>
       </c>
       <c r="B231" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C231" t="n">
-        <v>25.5900315944965</v>
+        <v>26.6220133276149</v>
       </c>
       <c r="D231" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="232">
@@ -3753,13 +3753,13 @@
         <v>43070</v>
       </c>
       <c r="B232" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C232" t="n">
-        <v>25.4923180492828</v>
+        <v>26.4844404657604</v>
       </c>
       <c r="D232" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="233">
@@ -3767,80 +3767,80 @@
         <v>44166</v>
       </c>
       <c r="B233" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C233" t="n">
-        <v>25.4588446997656</v>
+        <v>26.4188974793017</v>
       </c>
       <c r="D233" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>43800</v>
+        <v>42705</v>
       </c>
       <c r="B234" t="s">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C234" t="n">
-        <v>25.2394339494086</v>
+        <v>26.3071406569858</v>
       </c>
       <c r="D234" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="B235" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="C235" t="n">
-        <v>25.1567963055051</v>
+        <v>26.1674032924201</v>
       </c>
       <c r="D235" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>44531</v>
+        <v>43800</v>
       </c>
       <c r="B236" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="C236" t="n">
-        <v>25.1430474249778</v>
+        <v>26.1009708649337</v>
       </c>
       <c r="D236" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>45627</v>
+        <v>44166</v>
       </c>
       <c r="B237" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C237" t="n">
-        <v>25.1061270799575</v>
+        <v>26.0743936000392</v>
       </c>
       <c r="D237" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>43435</v>
+        <v>43070</v>
       </c>
       <c r="B238" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C238" t="n">
-        <v>25.0574098110388</v>
+        <v>25.993159556743</v>
       </c>
       <c r="D238" t="n">
         <v>16</v>
@@ -3848,170 +3848,170 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>43435</v>
+        <v>45627</v>
       </c>
       <c r="B239" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C239" t="n">
-        <v>24.907040734065</v>
+        <v>25.9046385493402</v>
       </c>
       <c r="D239" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>43435</v>
+        <v>43800</v>
       </c>
       <c r="B240" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C240" t="n">
-        <v>24.8889950819346</v>
+        <v>25.8859494309262</v>
       </c>
       <c r="D240" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>44166</v>
+        <v>45992</v>
       </c>
       <c r="B241" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="C241" t="n">
-        <v>24.8822443436395</v>
+        <v>25.8717285996602</v>
       </c>
       <c r="D241" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>43070</v>
+        <v>45992</v>
       </c>
       <c r="B242" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C242" t="n">
-        <v>24.7120361344884</v>
+        <v>25.7874457438368</v>
       </c>
       <c r="D242" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>44896</v>
+        <v>45627</v>
       </c>
       <c r="B243" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C243" t="n">
-        <v>24.6479850813341</v>
+        <v>25.7589910783215</v>
       </c>
       <c r="D243" t="n">
-        <v>39</v>
+        <v>23</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>42339</v>
+        <v>44896</v>
       </c>
       <c r="B244" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C244" t="n">
-        <v>24.6429701315188</v>
+        <v>25.7494716242528</v>
       </c>
       <c r="D244" t="n">
-        <v>7</v>
+        <v>38</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>45627</v>
+        <v>43435</v>
       </c>
       <c r="B245" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C245" t="n">
-        <v>24.5518016275257</v>
+        <v>25.5900315944965</v>
       </c>
       <c r="D245" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>44896</v>
+        <v>43070</v>
       </c>
       <c r="B246" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C246" t="n">
-        <v>24.5482210299248</v>
+        <v>25.4923180492828</v>
       </c>
       <c r="D246" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>45627</v>
+        <v>44166</v>
       </c>
       <c r="B247" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C247" t="n">
-        <v>24.5222176201784</v>
+        <v>25.4588446997656</v>
       </c>
       <c r="D247" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>43435</v>
+        <v>43800</v>
       </c>
       <c r="B248" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C248" t="n">
-        <v>24.4377792245822</v>
+        <v>25.2394339494086</v>
       </c>
       <c r="D248" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>43435</v>
+        <v>42339</v>
       </c>
       <c r="B249" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C249" t="n">
-        <v>24.2217179572168</v>
+        <v>25.1567963055051</v>
       </c>
       <c r="D249" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>45627</v>
+        <v>44531</v>
       </c>
       <c r="B250" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C250" t="n">
-        <v>24.1307790529207</v>
+        <v>25.1430474249778</v>
       </c>
       <c r="D250" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="251">
@@ -4019,39 +4019,41 @@
         <v>45627</v>
       </c>
       <c r="B251" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C251" t="n">
-        <v>24.1286664771613</v>
+        <v>25.1061270799575</v>
       </c>
       <c r="D251" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>42705</v>
+        <v>43435</v>
       </c>
       <c r="B252" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C252" t="n">
-        <v>23.9521935792085</v>
+        <v>25.0574098110388</v>
       </c>
       <c r="D252" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" s="1" t="n">
-        <v>44896</v>
-      </c>
-      <c r="B253"/>
+        <v>43435</v>
+      </c>
+      <c r="B253" t="s">
+        <v>10</v>
+      </c>
       <c r="C253" t="n">
-        <v>23.918286435976</v>
+        <v>24.907040734065</v>
       </c>
       <c r="D253" t="n">
-        <v>41</v>
+        <v>17</v>
       </c>
     </row>
     <row r="254">
@@ -4059,97 +4061,97 @@
         <v>43435</v>
       </c>
       <c r="B254" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C254" t="n">
-        <v>23.8767415061306</v>
+        <v>24.8889950819346</v>
       </c>
       <c r="D254" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" s="1" t="n">
-        <v>45261</v>
+        <v>44166</v>
       </c>
       <c r="B255" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="C255" t="n">
-        <v>23.7162743050638</v>
+        <v>24.8822443436395</v>
       </c>
       <c r="D255" t="n">
-        <v>38</v>
+        <v>31</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="1" t="n">
-        <v>44531</v>
+        <v>43070</v>
       </c>
       <c r="B256" t="s">
-        <v>44</v>
+        <v>13</v>
       </c>
       <c r="C256" t="n">
-        <v>23.7017306495826</v>
+        <v>24.7120361344884</v>
       </c>
       <c r="D256" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="1" t="n">
-        <v>43070</v>
+        <v>44896</v>
       </c>
       <c r="B257" t="s">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="C257" t="n">
-        <v>23.6617528806896</v>
+        <v>24.6479850813341</v>
       </c>
       <c r="D257" t="n">
-        <v>19</v>
+        <v>39</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="1" t="n">
-        <v>44896</v>
+        <v>42339</v>
       </c>
       <c r="B258" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C258" t="n">
-        <v>23.6600794803411</v>
+        <v>24.6429701315188</v>
       </c>
       <c r="D258" t="n">
-        <v>42</v>
+        <v>7</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="1" t="n">
-        <v>44531</v>
+        <v>45627</v>
       </c>
       <c r="B259" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C259" t="n">
-        <v>23.6567332027063</v>
+        <v>24.5518016275257</v>
       </c>
       <c r="D259" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="B260" t="s">
         <v>44</v>
       </c>
       <c r="C260" t="n">
-        <v>23.6488250008112</v>
+        <v>24.5482210299248</v>
       </c>
       <c r="D260" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="261">
@@ -4157,69 +4159,69 @@
         <v>45627</v>
       </c>
       <c r="B261" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C261" t="n">
-        <v>23.5309418879779</v>
+        <v>24.5234307505643</v>
       </c>
       <c r="D261" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B262" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C262" t="n">
-        <v>23.5141744012182</v>
+        <v>24.4377792245822</v>
       </c>
       <c r="D262" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="1" t="n">
-        <v>43800</v>
+        <v>43435</v>
       </c>
       <c r="B263" t="s">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="C263" t="n">
-        <v>23.4335124271156</v>
+        <v>24.2217179572168</v>
       </c>
       <c r="D263" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="1" t="n">
-        <v>42705</v>
+        <v>45627</v>
       </c>
       <c r="B264" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C264" t="n">
-        <v>23.4193591818584</v>
+        <v>24.1380386529147</v>
       </c>
       <c r="D264" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" s="1" t="n">
-        <v>43070</v>
+        <v>45627</v>
       </c>
       <c r="B265" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="C265" t="n">
-        <v>23.4193591818584</v>
+        <v>24.1307790529207</v>
       </c>
       <c r="D265" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="266">
@@ -4227,137 +4229,137 @@
         <v>42705</v>
       </c>
       <c r="B266" t="s">
-        <v>26</v>
+        <v>6</v>
       </c>
       <c r="C266" t="n">
-        <v>23.4116950320252</v>
+        <v>23.9521935792085</v>
       </c>
       <c r="D266" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" s="1" t="n">
-        <v>44166</v>
-      </c>
-      <c r="B267" t="s">
-        <v>36</v>
-      </c>
+        <v>44896</v>
+      </c>
+      <c r="B267"/>
       <c r="C267" t="n">
-        <v>23.3403056867848</v>
+        <v>23.918286435976</v>
       </c>
       <c r="D267" t="n">
-        <v>32</v>
+        <v>41</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" s="1" t="n">
-        <v>42705</v>
+        <v>43435</v>
       </c>
       <c r="B268" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="C268" t="n">
-        <v>23.2745064055576</v>
+        <v>23.8767415061306</v>
       </c>
       <c r="D268" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="1" t="n">
-        <v>44531</v>
+        <v>45261</v>
       </c>
       <c r="B269" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C269" t="n">
-        <v>23.2597876129012</v>
+        <v>23.7162743050638</v>
       </c>
       <c r="D269" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="1" t="n">
-        <v>45261</v>
-      </c>
-      <c r="B270"/>
+        <v>44531</v>
+      </c>
+      <c r="B270" t="s">
+        <v>44</v>
+      </c>
       <c r="C270" t="n">
-        <v>23.2236897339211</v>
+        <v>23.7017306495826</v>
       </c>
       <c r="D270" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="1" t="n">
-        <v>43800</v>
+        <v>43070</v>
       </c>
       <c r="B271" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C271" t="n">
-        <v>23.2083937241888</v>
+        <v>23.6617528806896</v>
       </c>
       <c r="D271" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="1" t="n">
-        <v>45627</v>
+        <v>44896</v>
       </c>
       <c r="B272" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C272" t="n">
-        <v>23.1854464196029</v>
+        <v>23.6600794803411</v>
       </c>
       <c r="D272" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="1" t="n">
-        <v>43435</v>
+        <v>45992</v>
       </c>
       <c r="B273" t="s">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="C273" t="n">
-        <v>23.1305297594228</v>
+        <v>23.6594153655837</v>
       </c>
       <c r="D273" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="1" t="n">
-        <v>42705</v>
+        <v>44531</v>
       </c>
       <c r="B274" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C274" t="n">
-        <v>23.1103300887345</v>
+        <v>23.6567332027063</v>
       </c>
       <c r="D274" t="n">
-        <v>17</v>
+        <v>39</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="1" t="n">
-        <v>44531</v>
+        <v>45261</v>
       </c>
       <c r="B275" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C275" t="n">
-        <v>22.9445542681529</v>
+        <v>23.6488250008112</v>
       </c>
       <c r="D275" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="276">
@@ -4365,195 +4367,193 @@
         <v>45627</v>
       </c>
       <c r="B276" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="C276" t="n">
-        <v>22.8551748520993</v>
+        <v>23.5309418879779</v>
       </c>
       <c r="D276" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="1" t="n">
-        <v>43070</v>
+        <v>42339</v>
       </c>
       <c r="B277" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="C277" t="n">
-        <v>22.8513067687133</v>
+        <v>23.5141744012182</v>
       </c>
       <c r="D277" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="1" t="n">
-        <v>45627</v>
+        <v>45992</v>
       </c>
       <c r="B278" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C278" t="n">
-        <v>22.7892523618868</v>
+        <v>23.4836803871099</v>
       </c>
       <c r="D278" t="n">
-        <v>32</v>
+        <v>16</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="1" t="n">
-        <v>43070</v>
+        <v>43800</v>
       </c>
       <c r="B279" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C279" t="n">
-        <v>22.7630425883826</v>
+        <v>23.4335124271156</v>
       </c>
       <c r="D279" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="1" t="n">
-        <v>44166</v>
+        <v>42705</v>
       </c>
       <c r="B280" t="s">
+        <v>11</v>
+      </c>
+      <c r="C280" t="n">
+        <v>23.4193591818584</v>
+      </c>
+      <c r="D280" t="n">
         <v>14</v>
-      </c>
-      <c r="C280" t="n">
-        <v>22.6587570188322</v>
-      </c>
-      <c r="D280" t="n">
-        <v>33</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="1" t="n">
-        <v>42705</v>
+        <v>43070</v>
       </c>
       <c r="B281" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="C281" t="n">
-        <v>22.5676516648772</v>
+        <v>23.4193591818584</v>
       </c>
       <c r="D281" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="1" t="n">
-        <v>43435</v>
+        <v>42705</v>
       </c>
       <c r="B282" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C282" t="n">
-        <v>22.4425960472978</v>
+        <v>23.4116950320252</v>
       </c>
       <c r="D282" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="1" t="n">
-        <v>42705</v>
+        <v>44166</v>
       </c>
       <c r="B283" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C283" t="n">
-        <v>22.3066828214843</v>
+        <v>23.3403056867848</v>
       </c>
       <c r="D283" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="1" t="n">
-        <v>43800</v>
+        <v>42705</v>
       </c>
       <c r="B284" t="s">
+        <v>37</v>
+      </c>
+      <c r="C284" t="n">
+        <v>23.2745064055576</v>
+      </c>
+      <c r="D284" t="n">
         <v>16</v>
-      </c>
-      <c r="C284" t="n">
-        <v>22.2685883152326</v>
-      </c>
-      <c r="D284" t="n">
-        <v>23</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" s="1" t="n">
-        <v>42339</v>
+        <v>44531</v>
       </c>
       <c r="B285" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C285" t="n">
-        <v>22.1616329157109</v>
+        <v>23.2597876129012</v>
       </c>
       <c r="D285" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" s="1" t="n">
         <v>45261</v>
       </c>
-      <c r="B286" t="s">
-        <v>45</v>
-      </c>
+      <c r="B286"/>
       <c r="C286" t="n">
-        <v>22.0846537112538</v>
+        <v>23.2236897339211</v>
       </c>
       <c r="D286" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" s="1" t="n">
-        <v>45261</v>
+        <v>45992</v>
       </c>
       <c r="B287" t="s">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="C287" t="n">
-        <v>22.0241016507671</v>
+        <v>23.2218528544956</v>
       </c>
       <c r="D287" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="1" t="n">
-        <v>43070</v>
+        <v>43800</v>
       </c>
       <c r="B288" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C288" t="n">
-        <v>21.9657495342343</v>
+        <v>23.2083937241888</v>
       </c>
       <c r="D288" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="1" t="n">
-        <v>45261</v>
+        <v>45627</v>
       </c>
       <c r="B289" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="C289" t="n">
-        <v>21.8614719352928</v>
+        <v>23.1854464196029</v>
       </c>
       <c r="D289" t="n">
-        <v>43</v>
+        <v>30</v>
       </c>
     </row>
     <row r="290">
@@ -4561,111 +4561,111 @@
         <v>43435</v>
       </c>
       <c r="B290" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="C290" t="n">
-        <v>21.7763560359393</v>
+        <v>23.1305297594228</v>
       </c>
       <c r="D290" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="1" t="n">
-        <v>42339</v>
+        <v>42705</v>
       </c>
       <c r="B291" t="s">
         <v>13</v>
       </c>
       <c r="C291" t="n">
-        <v>21.737439192374</v>
+        <v>23.1103300887345</v>
       </c>
       <c r="D291" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="1" t="n">
-        <v>43435</v>
+        <v>44531</v>
       </c>
       <c r="B292" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="C292" t="n">
-        <v>21.6648522594049</v>
+        <v>22.9445542681529</v>
       </c>
       <c r="D292" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="B293" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="C293" t="n">
-        <v>21.6428051165619</v>
+        <v>22.8551748520993</v>
       </c>
       <c r="D293" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="1" t="n">
-        <v>45261</v>
+        <v>43070</v>
       </c>
       <c r="B294" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="C294" t="n">
-        <v>21.6007451947626</v>
+        <v>22.8513067687133</v>
       </c>
       <c r="D294" t="n">
-        <v>44</v>
+        <v>21</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="B295" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C295" t="n">
-        <v>21.5724910869112</v>
+        <v>22.7942238392781</v>
       </c>
       <c r="D295" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="1" t="n">
-        <v>43800</v>
+        <v>43070</v>
       </c>
       <c r="B296" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="C296" t="n">
-        <v>21.5683925432009</v>
+        <v>22.7630425883826</v>
       </c>
       <c r="D296" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="1" t="n">
-        <v>43070</v>
+        <v>44166</v>
       </c>
       <c r="B297" t="s">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="C297" t="n">
-        <v>21.5648130260518</v>
+        <v>22.6587570188322</v>
       </c>
       <c r="D297" t="n">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="298">
@@ -4673,55 +4673,55 @@
         <v>42705</v>
       </c>
       <c r="B298" t="s">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="C298" t="n">
-        <v>21.5575316626246</v>
+        <v>22.5676516648772</v>
       </c>
       <c r="D298" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="B299" t="s">
         <v>17</v>
       </c>
       <c r="C299" t="n">
-        <v>21.4684937655982</v>
+        <v>22.5093904330211</v>
       </c>
       <c r="D299" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="1" t="n">
-        <v>43070</v>
+        <v>45992</v>
       </c>
       <c r="B300" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C300" t="n">
-        <v>21.4417762878326</v>
+        <v>22.5013827654767</v>
       </c>
       <c r="D300" t="n">
-        <v>25</v>
+        <v>19</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="1" t="n">
-        <v>45627</v>
+        <v>43435</v>
       </c>
       <c r="B301" t="s">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C301" t="n">
-        <v>21.3841188102879</v>
+        <v>22.4425960472978</v>
       </c>
       <c r="D301" t="n">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="302">
@@ -4729,220 +4729,220 @@
         <v>42705</v>
       </c>
       <c r="B302" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="C302" t="n">
-        <v>21.3449737622514</v>
+        <v>22.3066828214843</v>
       </c>
       <c r="D302" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="1" t="n">
-        <v>45261</v>
+        <v>43800</v>
       </c>
       <c r="B303" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>21.3345161126152</v>
+        <v>22.2685883152326</v>
       </c>
       <c r="D303" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="1" t="n">
-        <v>44896</v>
+        <v>42339</v>
       </c>
       <c r="B304" t="s">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="C304" t="n">
-        <v>21.3304291578296</v>
+        <v>22.1616329157109</v>
       </c>
       <c r="D304" t="n">
-        <v>43</v>
+        <v>9</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="1" t="n">
-        <v>43435</v>
+        <v>45261</v>
       </c>
       <c r="B305" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="C305" t="n">
-        <v>21.3074391273683</v>
+        <v>22.0846537112538</v>
       </c>
       <c r="D305" t="n">
-        <v>26</v>
+        <v>41</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="1" t="n">
-        <v>42339</v>
+        <v>45261</v>
       </c>
       <c r="B306" t="s">
-        <v>6</v>
+        <v>46</v>
       </c>
       <c r="C306" t="n">
-        <v>21.2114678379479</v>
+        <v>22.0241016507671</v>
       </c>
       <c r="D306" t="n">
-        <v>12</v>
+        <v>42</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="1" t="n">
-        <v>42705</v>
+        <v>43070</v>
       </c>
       <c r="B307" t="s">
         <v>22</v>
       </c>
       <c r="C307" t="n">
-        <v>21.1957851557812</v>
+        <v>21.9657495342343</v>
       </c>
       <c r="D307" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="1" t="n">
-        <v>45627</v>
+        <v>45261</v>
       </c>
       <c r="B308" t="s">
-        <v>32</v>
+        <v>41</v>
       </c>
       <c r="C308" t="n">
-        <v>21.1283834653235</v>
+        <v>21.8614719352928</v>
       </c>
       <c r="D308" t="n">
-        <v>34</v>
+        <v>43</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B309" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>21.0787026058546</v>
+        <v>21.7763560359393</v>
       </c>
       <c r="D309" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="1" t="n">
-        <v>44531</v>
+        <v>42339</v>
       </c>
       <c r="B310" t="s">
-        <v>47</v>
+        <v>13</v>
       </c>
       <c r="C310" t="n">
-        <v>20.8889727886314</v>
+        <v>21.737439192374</v>
       </c>
       <c r="D310" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="1" t="n">
-        <v>44531</v>
+        <v>43435</v>
       </c>
       <c r="B311" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="C311" t="n">
-        <v>20.8561395385504</v>
+        <v>21.6648522594049</v>
       </c>
       <c r="D311" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="1" t="n">
-        <v>43435</v>
+        <v>45992</v>
       </c>
       <c r="B312" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C312" t="n">
-        <v>20.5777241704896</v>
+        <v>21.6488765019486</v>
       </c>
       <c r="D312" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="1" t="n">
-        <v>45627</v>
+        <v>43800</v>
       </c>
       <c r="B313" t="s">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="C313" t="n">
-        <v>20.5513145189207</v>
+        <v>21.6428051165619</v>
       </c>
       <c r="D313" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="B314" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C314" t="n">
-        <v>20.4371471718139</v>
+        <v>21.6007451947626</v>
       </c>
       <c r="D314" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="1" t="n">
-        <v>42705</v>
+        <v>43800</v>
       </c>
       <c r="B315" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C315" t="n">
-        <v>20.3387117363738</v>
+        <v>21.5724910869112</v>
       </c>
       <c r="D315" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" s="1" t="n">
-        <v>45261</v>
+        <v>43800</v>
       </c>
       <c r="B316" t="s">
-        <v>49</v>
+        <v>25</v>
       </c>
       <c r="C316" t="n">
-        <v>20.2581450715024</v>
+        <v>21.5683925432009</v>
       </c>
       <c r="D316" t="n">
-        <v>46</v>
+        <v>26</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" s="1" t="n">
-        <v>42705</v>
+        <v>43070</v>
       </c>
       <c r="B317" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="C317" t="n">
-        <v>20.1153071297932</v>
+        <v>21.5648130260518</v>
       </c>
       <c r="D317" t="n">
         <v>24</v>
@@ -4950,490 +4950,492 @@
     </row>
     <row r="318">
       <c r="A318" s="1" t="n">
-        <v>42339</v>
+        <v>42705</v>
       </c>
       <c r="B318" t="s">
-        <v>47</v>
+        <v>8</v>
       </c>
       <c r="C318" t="n">
-        <v>20.0843605034397</v>
+        <v>21.5575316626246</v>
       </c>
       <c r="D318" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" s="1" t="n">
-        <v>43070</v>
+        <v>42339</v>
       </c>
       <c r="B319" t="s">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="C319" t="n">
-        <v>20.0454351843541</v>
+        <v>21.4684937655982</v>
       </c>
       <c r="D319" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" s="1" t="n">
-        <v>44896</v>
+        <v>43070</v>
       </c>
       <c r="B320" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
       <c r="C320" t="n">
-        <v>19.9915206243791</v>
+        <v>21.4417762878326</v>
       </c>
       <c r="D320" t="n">
-        <v>44</v>
+        <v>25</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" s="1" t="n">
-        <v>44896</v>
+        <v>45627</v>
       </c>
       <c r="B321" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C321" t="n">
-        <v>19.9821485446427</v>
+        <v>21.3841188102879</v>
       </c>
       <c r="D321" t="n">
-        <v>45</v>
+        <v>33</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" s="1" t="n">
-        <v>43070</v>
+        <v>42705</v>
       </c>
       <c r="B322" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C322" t="n">
-        <v>19.9605739980256</v>
+        <v>21.3449737622514</v>
       </c>
       <c r="D322" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" s="1" t="n">
-        <v>43070</v>
+        <v>45261</v>
       </c>
       <c r="B323" t="s">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="C323" t="n">
-        <v>19.9489742642647</v>
+        <v>21.3345161126152</v>
       </c>
       <c r="D323" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" s="1" t="n">
-        <v>45627</v>
+        <v>44896</v>
       </c>
       <c r="B324" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C324" t="n">
-        <v>19.875125624589</v>
+        <v>21.3304291578296</v>
       </c>
       <c r="D324" t="n">
-        <v>36</v>
+        <v>43</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B325" t="s">
-        <v>7</v>
+        <v>40</v>
       </c>
       <c r="C325" t="n">
-        <v>19.8596179620569</v>
+        <v>21.3074391273683</v>
       </c>
       <c r="D325" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" s="1" t="n">
-        <v>45261</v>
+        <v>42339</v>
       </c>
       <c r="B326" t="s">
-        <v>50</v>
+        <v>6</v>
       </c>
       <c r="C326" t="n">
-        <v>19.8423003126436</v>
+        <v>21.2114678379479</v>
       </c>
       <c r="D326" t="n">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" s="1" t="n">
-        <v>44166</v>
+        <v>42705</v>
       </c>
       <c r="B327" t="s">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="C327" t="n">
-        <v>19.8382772766122</v>
+        <v>21.1957851557812</v>
       </c>
       <c r="D327" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" s="1" t="n">
-        <v>44166</v>
+        <v>45627</v>
       </c>
       <c r="B328" t="s">
+        <v>32</v>
+      </c>
+      <c r="C328" t="n">
+        <v>21.1283834653235</v>
+      </c>
+      <c r="D328" t="n">
         <v>34</v>
-      </c>
-      <c r="C328" t="n">
-        <v>19.7892019789202</v>
-      </c>
-      <c r="D328" t="n">
-        <v>35</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" s="1" t="n">
-        <v>43070</v>
+        <v>42339</v>
       </c>
       <c r="B329" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C329" t="n">
-        <v>19.708980462907</v>
+        <v>21.0787026058546</v>
       </c>
       <c r="D329" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" s="1" t="n">
-        <v>42705</v>
+        <v>45992</v>
       </c>
       <c r="B330" t="s">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="C330" t="n">
-        <v>19.6773563351694</v>
+        <v>20.9838610029047</v>
       </c>
       <c r="D330" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="1" t="n">
-        <v>42339</v>
+        <v>44531</v>
       </c>
       <c r="B331" t="s">
-        <v>10</v>
+        <v>47</v>
       </c>
       <c r="C331" t="n">
-        <v>19.6750883905188</v>
+        <v>20.8889727886314</v>
       </c>
       <c r="D331" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="1" t="n">
-        <v>45627</v>
+        <v>44531</v>
       </c>
       <c r="B332" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C332" t="n">
-        <v>19.6618060176045</v>
+        <v>20.8561395385504</v>
       </c>
       <c r="D332" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="1" t="n">
-        <v>44896</v>
+        <v>45992</v>
       </c>
       <c r="B333" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C333" t="n">
-        <v>19.6586578425571</v>
+        <v>20.8148911609291</v>
       </c>
       <c r="D333" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="B334" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="C334" t="n">
-        <v>19.6074300333754</v>
+        <v>20.7651862832173</v>
       </c>
       <c r="D334" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="1" t="n">
-        <v>43070</v>
+        <v>45992</v>
       </c>
       <c r="B335" t="s">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C335" t="n">
-        <v>19.572706489692</v>
+        <v>20.7308068200616</v>
       </c>
       <c r="D335" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="1" t="n">
-        <v>43070</v>
+        <v>45992</v>
       </c>
       <c r="B336" t="s">
         <v>35</v>
       </c>
       <c r="C336" t="n">
-        <v>19.5028742677557</v>
+        <v>20.693309450333</v>
       </c>
       <c r="D336" t="n">
-        <v>31</v>
+        <v>25</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="1" t="n">
-        <v>43435</v>
+        <v>45992</v>
       </c>
       <c r="B337" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C337" t="n">
-        <v>19.4963746027227</v>
+        <v>20.6329410161538</v>
       </c>
       <c r="D337" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="1" t="n">
-        <v>44896</v>
+        <v>43435</v>
       </c>
       <c r="B338" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="C338" t="n">
-        <v>19.4702710289247</v>
+        <v>20.5777241704896</v>
       </c>
       <c r="D338" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="1" t="n">
-        <v>42705</v>
+        <v>45627</v>
       </c>
       <c r="B339" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C339" t="n">
-        <v>19.3912826530989</v>
+        <v>20.5513145189207</v>
       </c>
       <c r="D339" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="1" t="n">
-        <v>45627</v>
+        <v>43800</v>
       </c>
       <c r="B340" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C340" t="n">
-        <v>19.3291694956488</v>
+        <v>20.4371471718139</v>
       </c>
       <c r="D340" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="1" t="n">
-        <v>44531</v>
-      </c>
-      <c r="B341"/>
+        <v>42705</v>
+      </c>
+      <c r="B341" t="s">
+        <v>35</v>
+      </c>
       <c r="C341" t="n">
-        <v>19.2977083744806</v>
+        <v>20.3387117363738</v>
       </c>
       <c r="D341" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="B342" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C342" t="n">
-        <v>19.2488015918945</v>
+        <v>20.2581450715024</v>
       </c>
       <c r="D342" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="1" t="n">
-        <v>43800</v>
+        <v>45992</v>
       </c>
       <c r="B343" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C343" t="n">
-        <v>19.2200973725079</v>
+        <v>20.1415476980181</v>
       </c>
       <c r="D343" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="1" t="n">
-        <v>43070</v>
+        <v>42705</v>
       </c>
       <c r="B344" t="s">
-        <v>12</v>
+        <v>47</v>
       </c>
       <c r="C344" t="n">
-        <v>19.1588842191939</v>
+        <v>20.1153071297932</v>
       </c>
       <c r="D344" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="1" t="n">
-        <v>45627</v>
+        <v>42339</v>
       </c>
       <c r="B345" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C345" t="n">
-        <v>19.0989458405054</v>
+        <v>20.0843605034397</v>
       </c>
       <c r="D345" t="n">
-        <v>39</v>
+        <v>14</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="1" t="n">
-        <v>44531</v>
+        <v>43070</v>
       </c>
       <c r="B346" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C346" t="n">
-        <v>19.0437603533197</v>
+        <v>20.0454351843541</v>
       </c>
       <c r="D346" t="n">
-        <v>45</v>
+        <v>26</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="1" t="n">
-        <v>44166</v>
+        <v>44896</v>
       </c>
       <c r="B347" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C347" t="n">
-        <v>18.988674219022</v>
+        <v>19.9915206243791</v>
       </c>
       <c r="D347" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="1" t="n">
-        <v>44166</v>
+        <v>44896</v>
       </c>
       <c r="B348" t="s">
-        <v>18</v>
+        <v>49</v>
       </c>
       <c r="C348" t="n">
-        <v>18.943819097699</v>
+        <v>19.9821485446427</v>
       </c>
       <c r="D348" t="n">
-        <v>38</v>
+        <v>45</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="1" t="n">
-        <v>42705</v>
+        <v>45992</v>
       </c>
       <c r="B349" t="s">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C349" t="n">
-        <v>18.9286803668093</v>
+        <v>19.9643023621067</v>
       </c>
       <c r="D349" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="1" t="n">
-        <v>45627</v>
+        <v>43070</v>
       </c>
       <c r="B350" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="C350" t="n">
-        <v>18.916552124277</v>
+        <v>19.9605739980256</v>
       </c>
       <c r="D350" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="1" t="n">
-        <v>44896</v>
+        <v>43070</v>
       </c>
       <c r="B351" t="s">
-        <v>50</v>
+        <v>23</v>
       </c>
       <c r="C351" t="n">
-        <v>18.9068330375582</v>
+        <v>19.9489742642647</v>
       </c>
       <c r="D351" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="1" t="n">
-        <v>44166</v>
+        <v>45627</v>
       </c>
       <c r="B352" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="C352" t="n">
-        <v>18.8949924723971</v>
+        <v>19.875125624589</v>
       </c>
       <c r="D352" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="353">
@@ -5441,66 +5443,66 @@
         <v>42339</v>
       </c>
       <c r="B353" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C353" t="n">
-        <v>18.7876894470085</v>
+        <v>19.8596179620569</v>
       </c>
       <c r="D353" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="B354" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C354" t="n">
-        <v>18.7815053138434</v>
+        <v>19.8423003126436</v>
       </c>
       <c r="D354" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="1" t="n">
-        <v>42705</v>
+        <v>44166</v>
       </c>
       <c r="B355" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="C355" t="n">
-        <v>18.6263711989808</v>
+        <v>19.8382772766122</v>
       </c>
       <c r="D355" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="1" t="n">
-        <v>45627</v>
+        <v>44166</v>
       </c>
       <c r="B356" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C356" t="n">
-        <v>18.5557391860794</v>
+        <v>19.7892019789202</v>
       </c>
       <c r="D356" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="1" t="n">
-        <v>43435</v>
+        <v>43070</v>
       </c>
       <c r="B357" t="s">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>18.5126491464681</v>
+        <v>19.708980462907</v>
       </c>
       <c r="D357" t="n">
         <v>29</v>
@@ -5508,55 +5510,55 @@
     </row>
     <row r="358">
       <c r="A358" s="1" t="n">
-        <v>43435</v>
+        <v>42705</v>
       </c>
       <c r="B358" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C358" t="n">
-        <v>18.4839529409893</v>
+        <v>19.6773563351694</v>
       </c>
       <c r="D358" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="1" t="n">
-        <v>43800</v>
+        <v>42339</v>
       </c>
       <c r="B359" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C359" t="n">
-        <v>18.390460649869</v>
+        <v>19.6750883905188</v>
       </c>
       <c r="D359" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="1" t="n">
-        <v>42705</v>
+        <v>45627</v>
       </c>
       <c r="B360" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C360" t="n">
-        <v>18.376401498656</v>
+        <v>19.6618060176045</v>
       </c>
       <c r="D360" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="1" t="n">
-        <v>44531</v>
+        <v>44896</v>
       </c>
       <c r="B361" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="C361" t="n">
-        <v>18.3694783205756</v>
+        <v>19.6586578425571</v>
       </c>
       <c r="D361" t="n">
         <v>46</v>
@@ -5564,56 +5566,58 @@
     </row>
     <row r="362">
       <c r="A362" s="1" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B362"/>
+        <v>42339</v>
+      </c>
+      <c r="B362" t="s">
+        <v>37</v>
+      </c>
       <c r="C362" t="n">
-        <v>18.3615128195371</v>
+        <v>19.6074300333754</v>
       </c>
       <c r="D362" t="n">
-        <v>42</v>
+        <v>17</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="1" t="n">
-        <v>42339</v>
+        <v>43070</v>
       </c>
       <c r="B363" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C363" t="n">
-        <v>18.2871106770385</v>
+        <v>19.572706489692</v>
       </c>
       <c r="D363" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="1" t="n">
-        <v>42705</v>
+        <v>43070</v>
       </c>
       <c r="B364" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C364" t="n">
-        <v>18.2552649809878</v>
+        <v>19.5028742677557</v>
       </c>
       <c r="D364" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B365" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="C365" t="n">
-        <v>18.2482292404175</v>
+        <v>19.4963746027227</v>
       </c>
       <c r="D365" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
     </row>
     <row r="366">
@@ -5621,108 +5625,106 @@
         <v>44896</v>
       </c>
       <c r="B366" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="C366" t="n">
-        <v>18.2325071378326</v>
+        <v>19.4702710289247</v>
       </c>
       <c r="D366" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="1" t="n">
-        <v>43070</v>
+        <v>45992</v>
       </c>
       <c r="B367" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C367" t="n">
-        <v>18.1717284249165</v>
+        <v>19.4581594913185</v>
       </c>
       <c r="D367" t="n">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="1" t="n">
-        <v>43800</v>
+        <v>42705</v>
       </c>
       <c r="B368" t="s">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="C368" t="n">
-        <v>18.0718553273248</v>
+        <v>19.3912826530989</v>
       </c>
       <c r="D368" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="B369" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="C369" t="n">
-        <v>18.066348840117</v>
+        <v>19.3291694956488</v>
       </c>
       <c r="D369" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="1" t="n">
-        <v>45627</v>
-      </c>
-      <c r="B370" t="s">
-        <v>38</v>
-      </c>
+        <v>44531</v>
+      </c>
+      <c r="B370"/>
       <c r="C370" t="n">
-        <v>18.0250950803375</v>
+        <v>19.2977083744806</v>
       </c>
       <c r="D370" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="1" t="n">
-        <v>45627</v>
+        <v>44166</v>
       </c>
       <c r="B371" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C371" t="n">
-        <v>17.9949735512528</v>
+        <v>19.2488015918945</v>
       </c>
       <c r="D371" t="n">
-        <v>44</v>
+        <v>36</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="1" t="n">
-        <v>44166</v>
+        <v>43800</v>
       </c>
       <c r="B372" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
       <c r="C372" t="n">
-        <v>17.9304306033354</v>
+        <v>19.2200973725079</v>
       </c>
       <c r="D372" t="n">
-        <v>41</v>
+        <v>28</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="1" t="n">
-        <v>43800</v>
+        <v>43070</v>
       </c>
       <c r="B373" t="s">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="C373" t="n">
-        <v>17.9202302737939</v>
+        <v>19.1588842191939</v>
       </c>
       <c r="D373" t="n">
         <v>32</v>
@@ -5730,156 +5732,156 @@
     </row>
     <row r="374">
       <c r="A374" s="1" t="n">
-        <v>42339</v>
+        <v>45627</v>
       </c>
       <c r="B374" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="C374" t="n">
-        <v>17.8974949581189</v>
+        <v>19.0989458405054</v>
       </c>
       <c r="D374" t="n">
-        <v>21</v>
+        <v>39</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="1" t="n">
-        <v>43435</v>
+        <v>45992</v>
       </c>
       <c r="B375" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="C375" t="n">
-        <v>17.8058709223796</v>
+        <v>19.0650488597299</v>
       </c>
       <c r="D375" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="1" t="n">
-        <v>43800</v>
+        <v>44531</v>
       </c>
       <c r="B376" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C376" t="n">
-        <v>17.7943101532786</v>
+        <v>19.0437603533197</v>
       </c>
       <c r="D376" t="n">
-        <v>33</v>
+        <v>45</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="1" t="n">
-        <v>44896</v>
+        <v>44166</v>
       </c>
       <c r="B377" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C377" t="n">
-        <v>17.7183578885654</v>
+        <v>18.988674219022</v>
       </c>
       <c r="D377" t="n">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="1" t="n">
-        <v>42339</v>
+        <v>44166</v>
       </c>
       <c r="B378" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="C378" t="n">
-        <v>17.6991611542002</v>
+        <v>18.943819097699</v>
       </c>
       <c r="D378" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" s="1" t="n">
-        <v>44531</v>
+        <v>42705</v>
       </c>
       <c r="B379" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="C379" t="n">
-        <v>17.5859643315265</v>
+        <v>18.9286803668093</v>
       </c>
       <c r="D379" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" s="1" t="n">
-        <v>44166</v>
+        <v>45627</v>
       </c>
       <c r="B380" t="s">
         <v>43</v>
       </c>
       <c r="C380" t="n">
-        <v>17.5801588896266</v>
+        <v>18.916552124277</v>
       </c>
       <c r="D380" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" s="1" t="n">
-        <v>43435</v>
+        <v>44896</v>
       </c>
       <c r="B381" t="s">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="C381" t="n">
-        <v>17.5427070563617</v>
+        <v>18.9068330375582</v>
       </c>
       <c r="D381" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" s="1" t="n">
-        <v>44531</v>
+        <v>44166</v>
       </c>
       <c r="B382" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C382" t="n">
-        <v>17.5328253452297</v>
+        <v>18.8949924723971</v>
       </c>
       <c r="D382" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" s="1" t="n">
-        <v>45627</v>
+        <v>45992</v>
       </c>
       <c r="B383" t="s">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="C383" t="n">
-        <v>17.5294049595871</v>
+        <v>18.8755619673734</v>
       </c>
       <c r="D383" t="n">
-        <v>45</v>
+        <v>31</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" s="1" t="n">
-        <v>42705</v>
+        <v>42339</v>
       </c>
       <c r="B384" t="s">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C384" t="n">
-        <v>17.5283408813902</v>
+        <v>18.7876894470085</v>
       </c>
       <c r="D384" t="n">
-        <v>31</v>
+        <v>18</v>
       </c>
     </row>
     <row r="385">
@@ -5887,27 +5889,27 @@
         <v>44166</v>
       </c>
       <c r="B385" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C385" t="n">
-        <v>17.5152304466731</v>
+        <v>18.7815053138434</v>
       </c>
       <c r="D385" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" s="1" t="n">
-        <v>44531</v>
+        <v>42705</v>
       </c>
       <c r="B386" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="C386" t="n">
-        <v>17.5152304466731</v>
+        <v>18.6263711989808</v>
       </c>
       <c r="D386" t="n">
-        <v>49</v>
+        <v>28</v>
       </c>
     </row>
     <row r="387">
@@ -5915,69 +5917,69 @@
         <v>45627</v>
       </c>
       <c r="B387" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C387" t="n">
-        <v>17.4204794782559</v>
+        <v>18.5557391860794</v>
       </c>
       <c r="D387" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" s="1" t="n">
-        <v>45261</v>
+        <v>43435</v>
       </c>
       <c r="B388" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="C388" t="n">
-        <v>17.1971676896819</v>
+        <v>18.5126491464681</v>
       </c>
       <c r="D388" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" s="1" t="n">
-        <v>42705</v>
+        <v>43435</v>
       </c>
       <c r="B389" t="s">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="C389" t="n">
-        <v>17.1493726105815</v>
+        <v>18.4839529409893</v>
       </c>
       <c r="D389" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" s="1" t="n">
-        <v>44166</v>
+        <v>43800</v>
       </c>
       <c r="B390" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C390" t="n">
-        <v>17.0973775483492</v>
+        <v>18.390460649869</v>
       </c>
       <c r="D390" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" s="1" t="n">
-        <v>45261</v>
+        <v>42705</v>
       </c>
       <c r="B391" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C391" t="n">
-        <v>17.0689939868903</v>
+        <v>18.376401498656</v>
       </c>
       <c r="D391" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
     </row>
     <row r="392">
@@ -5985,97 +5987,95 @@
         <v>44531</v>
       </c>
       <c r="B392" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C392" t="n">
-        <v>17.0185750193304</v>
+        <v>18.3694783205756</v>
       </c>
       <c r="D392" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" s="1" t="n">
-        <v>43070</v>
-      </c>
-      <c r="B393" t="s">
-        <v>38</v>
-      </c>
+        <v>45627</v>
+      </c>
+      <c r="B393"/>
       <c r="C393" t="n">
-        <v>16.9531437245579</v>
+        <v>18.3615128195371</v>
       </c>
       <c r="D393" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" s="1" t="n">
-        <v>42705</v>
+        <v>42339</v>
       </c>
       <c r="B394" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C394" t="n">
-        <v>16.8612672404273</v>
+        <v>18.2871106770385</v>
       </c>
       <c r="D394" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" s="1" t="n">
-        <v>43800</v>
+        <v>42705</v>
       </c>
       <c r="B395" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="C395" t="n">
-        <v>16.8558883465956</v>
+        <v>18.2552649809878</v>
       </c>
       <c r="D395" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" s="1" t="n">
-        <v>43435</v>
+        <v>42339</v>
       </c>
       <c r="B396" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C396" t="n">
-        <v>16.708459175956</v>
+        <v>18.2482292404175</v>
       </c>
       <c r="D396" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" s="1" t="n">
-        <v>45627</v>
+        <v>44896</v>
       </c>
       <c r="B397" t="s">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="C397" t="n">
-        <v>16.5485741094693</v>
+        <v>18.2325071378326</v>
       </c>
       <c r="D397" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" s="1" t="n">
-        <v>42339</v>
+        <v>43070</v>
       </c>
       <c r="B398" t="s">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="C398" t="n">
-        <v>16.441311989521</v>
+        <v>18.1717284249165</v>
       </c>
       <c r="D398" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
     </row>
     <row r="399">
@@ -6083,111 +6083,111 @@
         <v>43800</v>
       </c>
       <c r="B399" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C399" t="n">
-        <v>16.4230040733251</v>
+        <v>18.0718553273248</v>
       </c>
       <c r="D399" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" s="1" t="n">
-        <v>45261</v>
+        <v>43800</v>
       </c>
       <c r="B400" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="C400" t="n">
-        <v>16.4221872801754</v>
+        <v>18.066348840117</v>
       </c>
       <c r="D400" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" s="1" t="n">
-        <v>43070</v>
+        <v>45992</v>
       </c>
       <c r="B401" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C401" t="n">
-        <v>16.147508591495</v>
+        <v>18.058461447301</v>
       </c>
       <c r="D401" t="n">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" s="1" t="n">
-        <v>44166</v>
+        <v>45627</v>
       </c>
       <c r="B402" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C402" t="n">
-        <v>16.1317881831412</v>
+        <v>18.0250950803375</v>
       </c>
       <c r="D402" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" s="1" t="n">
-        <v>42705</v>
+        <v>45627</v>
       </c>
       <c r="B403" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C403" t="n">
-        <v>16.127885460798</v>
+        <v>17.9949735512528</v>
       </c>
       <c r="D403" t="n">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" s="1" t="n">
-        <v>43800</v>
+        <v>45992</v>
       </c>
       <c r="B404" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C404" t="n">
-        <v>16.1270892697374</v>
+        <v>17.9393669859033</v>
       </c>
       <c r="D404" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" s="1" t="n">
-        <v>42339</v>
+        <v>44166</v>
       </c>
       <c r="B405" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="C405" t="n">
-        <v>15.9596400740409</v>
+        <v>17.9304306033354</v>
       </c>
       <c r="D405" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" s="1" t="n">
-        <v>42339</v>
+        <v>43800</v>
       </c>
       <c r="B406" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="C406" t="n">
-        <v>15.9544673375636</v>
+        <v>17.9202302737939</v>
       </c>
       <c r="D406" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
     </row>
     <row r="407">
@@ -6195,55 +6195,55 @@
         <v>42339</v>
       </c>
       <c r="B407" t="s">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="C407" t="n">
-        <v>15.9526808191815</v>
+        <v>17.8974949581189</v>
       </c>
       <c r="D407" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" s="1" t="n">
-        <v>44166</v>
+        <v>43435</v>
       </c>
       <c r="B408" t="s">
-        <v>51</v>
+        <v>35</v>
       </c>
       <c r="C408" t="n">
-        <v>15.9049530351305</v>
+        <v>17.8058709223796</v>
       </c>
       <c r="D408" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" s="1" t="n">
-        <v>45627</v>
+        <v>43800</v>
       </c>
       <c r="B409" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="C409" t="n">
-        <v>15.8630324552078</v>
+        <v>17.7943101532786</v>
       </c>
       <c r="D409" t="n">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" s="1" t="n">
-        <v>42705</v>
+        <v>44896</v>
       </c>
       <c r="B410" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C410" t="n">
-        <v>15.7996308525777</v>
+        <v>17.7183578885654</v>
       </c>
       <c r="D410" t="n">
-        <v>35</v>
+        <v>50</v>
       </c>
     </row>
     <row r="411">
@@ -6251,41 +6251,41 @@
         <v>42339</v>
       </c>
       <c r="B411" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C411" t="n">
-        <v>15.7077665627199</v>
+        <v>17.6991611542002</v>
       </c>
       <c r="D411" t="n">
-        <v>27</v>
+        <v>22</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" s="1" t="n">
-        <v>43800</v>
+        <v>45992</v>
       </c>
       <c r="B412" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="C412" t="n">
-        <v>15.6529562304845</v>
+        <v>17.6328361220802</v>
       </c>
       <c r="D412" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" s="1" t="n">
-        <v>45627</v>
+        <v>44531</v>
       </c>
       <c r="B413" t="s">
         <v>51</v>
       </c>
       <c r="C413" t="n">
-        <v>15.5170273513469</v>
+        <v>17.5859643315265</v>
       </c>
       <c r="D413" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="414">
@@ -6293,248 +6293,248 @@
         <v>44166</v>
       </c>
       <c r="B414" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C414" t="n">
-        <v>15.4558055041435</v>
+        <v>17.5801588896266</v>
       </c>
       <c r="D414" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B415" t="s">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="C415" t="n">
-        <v>15.4292847825172</v>
+        <v>17.5427070563617</v>
       </c>
       <c r="D415" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" s="1" t="n">
-        <v>42339</v>
+        <v>44531</v>
       </c>
       <c r="B416" t="s">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="C416" t="n">
-        <v>15.4103996264251</v>
+        <v>17.5328253452297</v>
       </c>
       <c r="D416" t="n">
-        <v>29</v>
+        <v>48</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" s="1" t="n">
-        <v>43070</v>
+        <v>45627</v>
       </c>
       <c r="B417" t="s">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="C417" t="n">
-        <v>15.3333882954786</v>
+        <v>17.5294049595871</v>
       </c>
       <c r="D417" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" s="1" t="n">
-        <v>43435</v>
+        <v>42705</v>
       </c>
       <c r="B418" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C418" t="n">
-        <v>15.267748790789</v>
+        <v>17.5283408813902</v>
       </c>
       <c r="D418" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" s="1" t="n">
-        <v>44896</v>
+        <v>44166</v>
       </c>
       <c r="B419" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="C419" t="n">
-        <v>14.8784715122881</v>
+        <v>17.5152304466731</v>
       </c>
       <c r="D419" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" s="1" t="n">
-        <v>42339</v>
+        <v>44531</v>
       </c>
       <c r="B420" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="C420" t="n">
-        <v>14.8680245674946</v>
+        <v>17.5152304466731</v>
       </c>
       <c r="D420" t="n">
-        <v>30</v>
+        <v>49</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" s="1" t="n">
-        <v>42339</v>
+        <v>45627</v>
       </c>
       <c r="B421" t="s">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="C421" t="n">
-        <v>14.8258583805455</v>
+        <v>17.4204794782559</v>
       </c>
       <c r="D421" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" s="1" t="n">
-        <v>44531</v>
+        <v>45992</v>
       </c>
       <c r="B422" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C422" t="n">
-        <v>14.8155604276696</v>
+        <v>17.2223397100048</v>
       </c>
       <c r="D422" t="n">
-        <v>51</v>
+        <v>35</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" s="1" t="n">
-        <v>42705</v>
+        <v>45261</v>
       </c>
       <c r="B423" t="s">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="C423" t="n">
-        <v>14.8068852016188</v>
+        <v>17.1971676896819</v>
       </c>
       <c r="D423" t="n">
-        <v>36</v>
+        <v>48</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" s="1" t="n">
-        <v>43435</v>
+        <v>45992</v>
       </c>
       <c r="B424" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C424" t="n">
-        <v>14.8068852016188</v>
+        <v>17.1714829096765</v>
       </c>
       <c r="D424" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" s="1" t="n">
-        <v>43800</v>
+        <v>42705</v>
       </c>
       <c r="B425" t="s">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="C425" t="n">
-        <v>14.7868758972922</v>
+        <v>17.1493726105815</v>
       </c>
       <c r="D425" t="n">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" s="1" t="n">
-        <v>42705</v>
+        <v>44166</v>
       </c>
       <c r="B426" t="s">
-        <v>14</v>
+        <v>48</v>
       </c>
       <c r="C426" t="n">
-        <v>14.6638653476452</v>
+        <v>17.0973775483492</v>
       </c>
       <c r="D426" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" s="1" t="n">
-        <v>43435</v>
+        <v>45261</v>
       </c>
       <c r="B427" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C427" t="n">
-        <v>14.5855033856256</v>
+        <v>17.0689939868903</v>
       </c>
       <c r="D427" t="n">
-        <v>36</v>
+        <v>49</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" s="1" t="n">
-        <v>43800</v>
+        <v>44531</v>
       </c>
       <c r="B428" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C428" t="n">
-        <v>14.5726166181925</v>
+        <v>17.0185750193304</v>
       </c>
       <c r="D428" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" s="1" t="n">
-        <v>44166</v>
+        <v>43070</v>
       </c>
       <c r="B429" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C429" t="n">
-        <v>14.5643046518575</v>
+        <v>16.9531437245579</v>
       </c>
       <c r="D429" t="n">
-        <v>48</v>
+        <v>34</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="B430" t="s">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="C430" t="n">
-        <v>14.5588421401419</v>
+        <v>16.887852851576</v>
       </c>
       <c r="D430" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" s="1" t="n">
-        <v>42339</v>
+        <v>42705</v>
       </c>
       <c r="B431" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C431" t="n">
-        <v>14.5377256710888</v>
+        <v>16.8612672404273</v>
       </c>
       <c r="D431" t="n">
         <v>33</v>
@@ -6545,97 +6545,97 @@
         <v>43800</v>
       </c>
       <c r="B432" t="s">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="C432" t="n">
-        <v>14.4990334373857</v>
+        <v>16.8558883465956</v>
       </c>
       <c r="D432" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="B433" t="s">
-        <v>16</v>
+        <v>51</v>
       </c>
       <c r="C433" t="n">
-        <v>14.4913183023972</v>
+        <v>16.8101129639591</v>
       </c>
       <c r="D433" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B434" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="C434" t="n">
-        <v>14.4066991150885</v>
+        <v>16.708459175956</v>
       </c>
       <c r="D434" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" s="1" t="n">
-        <v>43435</v>
+        <v>45627</v>
       </c>
       <c r="B435" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="C435" t="n">
-        <v>14.4030437323642</v>
+        <v>16.5485741094693</v>
       </c>
       <c r="D435" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" s="1" t="n">
-        <v>44166</v>
+        <v>42339</v>
       </c>
       <c r="B436" t="s">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="C436" t="n">
-        <v>14.3923372618686</v>
+        <v>16.441311989521</v>
       </c>
       <c r="D436" t="n">
-        <v>49</v>
+        <v>23</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" s="1" t="n">
-        <v>43070</v>
+        <v>43800</v>
       </c>
       <c r="B437" t="s">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="C437" t="n">
-        <v>14.2674094628876</v>
+        <v>16.4230040733251</v>
       </c>
       <c r="D437" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" s="1" t="n">
-        <v>43435</v>
+        <v>45261</v>
       </c>
       <c r="B438" t="s">
-        <v>12</v>
+        <v>51</v>
       </c>
       <c r="C438" t="n">
-        <v>14.2672542057827</v>
+        <v>16.4221872801754</v>
       </c>
       <c r="D438" t="n">
-        <v>38</v>
+        <v>50</v>
       </c>
     </row>
     <row r="439">
@@ -6643,279 +6643,279 @@
         <v>43070</v>
       </c>
       <c r="B439" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C439" t="n">
-        <v>14.1369366888101</v>
+        <v>16.147508591495</v>
       </c>
       <c r="D439" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" s="1" t="n">
-        <v>45261</v>
+        <v>44166</v>
       </c>
       <c r="B440" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="C440" t="n">
-        <v>14.0606274122469</v>
+        <v>16.1317881831412</v>
       </c>
       <c r="D440" t="n">
-        <v>51</v>
+        <v>45</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" s="1" t="n">
-        <v>43435</v>
+        <v>42705</v>
       </c>
       <c r="B441" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C441" t="n">
-        <v>13.9245997875117</v>
+        <v>16.127885460798</v>
       </c>
       <c r="D441" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" s="1" t="n">
-        <v>43070</v>
+        <v>43800</v>
       </c>
       <c r="B442" t="s">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C442" t="n">
-        <v>13.8975079429074</v>
+        <v>16.1270892697374</v>
       </c>
       <c r="D442" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" s="1" t="n">
-        <v>43800</v>
+        <v>45992</v>
       </c>
       <c r="B443" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C443" t="n">
-        <v>13.8965504106184</v>
+        <v>16.1181971686068</v>
       </c>
       <c r="D443" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="B444" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="C444" t="n">
-        <v>13.7262490774802</v>
+        <v>16.0942533978034</v>
       </c>
       <c r="D444" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" s="1" t="n">
-        <v>42705</v>
+        <v>45992</v>
       </c>
       <c r="B445" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C445" t="n">
-        <v>13.6911093100919</v>
+        <v>16.0485649985436</v>
       </c>
       <c r="D445" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" s="1" t="n">
-        <v>45627</v>
+        <v>45992</v>
       </c>
       <c r="B446" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C446" t="n">
-        <v>13.4315165660614</v>
+        <v>16.0168524578234</v>
       </c>
       <c r="D446" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" s="1" t="n">
-        <v>43435</v>
+        <v>42339</v>
       </c>
       <c r="B447" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C447" t="n">
-        <v>13.4134312053817</v>
+        <v>15.9596400740409</v>
       </c>
       <c r="D447" t="n">
-        <v>40</v>
+        <v>24</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" s="1" t="n">
-        <v>43435</v>
+        <v>42339</v>
       </c>
       <c r="B448" t="s">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="C448" t="n">
-        <v>13.2155124445679</v>
+        <v>15.9544673375636</v>
       </c>
       <c r="D448" t="n">
-        <v>41</v>
+        <v>25</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" s="1" t="n">
-        <v>44166</v>
+        <v>42339</v>
       </c>
       <c r="B449" t="s">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="C449" t="n">
-        <v>13.1798722275871</v>
+        <v>15.9526808191815</v>
       </c>
       <c r="D449" t="n">
-        <v>50</v>
+        <v>26</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" s="1" t="n">
-        <v>43800</v>
+        <v>44166</v>
       </c>
       <c r="B450" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C450" t="n">
-        <v>12.9686611080864</v>
+        <v>15.9049530351305</v>
       </c>
       <c r="D450" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="B451" t="s">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="C451" t="n">
-        <v>12.9599989632001</v>
+        <v>15.8630324552078</v>
       </c>
       <c r="D451" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" s="1" t="n">
-        <v>43435</v>
+        <v>42705</v>
       </c>
       <c r="B452" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="C452" t="n">
-        <v>12.9404274481995</v>
+        <v>15.7996308525777</v>
       </c>
       <c r="D452" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" s="1" t="n">
-        <v>45627</v>
+        <v>42339</v>
       </c>
       <c r="B453" t="s">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="C453" t="n">
-        <v>12.9394549928168</v>
+        <v>15.7077665627199</v>
       </c>
       <c r="D453" t="n">
-        <v>51</v>
+        <v>27</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" s="1" t="n">
-        <v>43070</v>
+        <v>43800</v>
       </c>
       <c r="B454" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="C454" t="n">
-        <v>12.9166374570342</v>
+        <v>15.6529562304845</v>
       </c>
       <c r="D454" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="B455" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C455" t="n">
-        <v>12.8945117618356</v>
+        <v>15.5170273513469</v>
       </c>
       <c r="D455" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" s="1" t="n">
-        <v>42705</v>
+        <v>44166</v>
       </c>
       <c r="B456" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="C456" t="n">
-        <v>12.8933713483878</v>
+        <v>15.4558055041435</v>
       </c>
       <c r="D456" t="n">
-        <v>39</v>
+        <v>47</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" s="1" t="n">
-        <v>42705</v>
+        <v>42339</v>
       </c>
       <c r="B457" t="s">
-        <v>48</v>
+        <v>23</v>
       </c>
       <c r="C457" t="n">
-        <v>12.839664851484</v>
+        <v>15.4292847825172</v>
       </c>
       <c r="D457" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" s="1" t="n">
-        <v>43070</v>
+        <v>42339</v>
       </c>
       <c r="B458" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C458" t="n">
-        <v>12.8384374351906</v>
+        <v>15.4103996264251</v>
       </c>
       <c r="D458" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="459">
@@ -6923,66 +6923,66 @@
         <v>43070</v>
       </c>
       <c r="B459" t="s">
+        <v>14</v>
+      </c>
+      <c r="C459" t="n">
+        <v>15.3333882954786</v>
+      </c>
+      <c r="D459" t="n">
         <v>36</v>
-      </c>
-      <c r="C459" t="n">
-        <v>12.7435179708061</v>
-      </c>
-      <c r="D459" t="n">
-        <v>42</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" s="1" t="n">
-        <v>43070</v>
+        <v>43435</v>
       </c>
       <c r="B460" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C460" t="n">
-        <v>12.6925964845311</v>
+        <v>15.267748790789</v>
       </c>
       <c r="D460" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="B461" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="C461" t="n">
-        <v>12.6733479492627</v>
+        <v>15.2649987788942</v>
       </c>
       <c r="D461" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" s="1" t="n">
-        <v>42705</v>
+        <v>45992</v>
       </c>
       <c r="B462" t="s">
-        <v>49</v>
+        <v>40</v>
       </c>
       <c r="C462" t="n">
-        <v>12.5854416248026</v>
+        <v>15.2162568585269</v>
       </c>
       <c r="D462" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" s="1" t="n">
-        <v>43800</v>
+        <v>45992</v>
       </c>
       <c r="B463" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C463" t="n">
-        <v>12.4861048728758</v>
+        <v>15.1330137986797</v>
       </c>
       <c r="D463" t="n">
         <v>45</v>
@@ -6990,30 +6990,30 @@
     </row>
     <row r="464">
       <c r="A464" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="B464" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C464" t="n">
-        <v>12.3098757107236</v>
+        <v>15.0922053713769</v>
       </c>
       <c r="D464" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" s="1" t="n">
-        <v>43800</v>
+        <v>44896</v>
       </c>
       <c r="B465" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="C465" t="n">
-        <v>12.3018931771004</v>
+        <v>14.8784715122881</v>
       </c>
       <c r="D465" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="466">
@@ -7021,13 +7021,13 @@
         <v>42339</v>
       </c>
       <c r="B466" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="C466" t="n">
-        <v>12.1523815884925</v>
+        <v>14.8680245674946</v>
       </c>
       <c r="D466" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="467">
@@ -7035,69 +7035,69 @@
         <v>42339</v>
       </c>
       <c r="B467" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C467" t="n">
-        <v>12.0693382213562</v>
+        <v>14.8258583805455</v>
       </c>
       <c r="D467" t="n">
-        <v>40</v>
+        <v>31</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" s="1" t="n">
-        <v>42705</v>
+        <v>44531</v>
       </c>
       <c r="B468" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="C468" t="n">
-        <v>12.0515966490022</v>
+        <v>14.8155604276696</v>
       </c>
       <c r="D468" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" s="1" t="n">
-        <v>43800</v>
+        <v>42705</v>
       </c>
       <c r="B469" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="C469" t="n">
-        <v>12.0413437208218</v>
+        <v>14.8068852016188</v>
       </c>
       <c r="D469" t="n">
-        <v>47</v>
+        <v>36</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B470" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C470" t="n">
-        <v>11.8131469153782</v>
+        <v>14.8068852016188</v>
       </c>
       <c r="D470" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" s="1" t="n">
-        <v>42339</v>
+        <v>43800</v>
       </c>
       <c r="B471" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="C471" t="n">
-        <v>11.8126513495954</v>
+        <v>14.7868758972922</v>
       </c>
       <c r="D471" t="n">
-        <v>42</v>
+        <v>38</v>
       </c>
     </row>
     <row r="472">
@@ -7105,209 +7105,209 @@
         <v>42705</v>
       </c>
       <c r="B472" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C472" t="n">
-        <v>11.7893780081038</v>
+        <v>14.6638653476452</v>
       </c>
       <c r="D472" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B473" t="s">
         <v>45</v>
       </c>
       <c r="C473" t="n">
-        <v>11.764722070481</v>
+        <v>14.5855033856256</v>
       </c>
       <c r="D473" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" s="1" t="n">
-        <v>42705</v>
+        <v>43800</v>
       </c>
       <c r="B474" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C474" t="n">
-        <v>11.7097835947343</v>
+        <v>14.5726166181925</v>
       </c>
       <c r="D474" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" s="1" t="n">
-        <v>42339</v>
+        <v>44166</v>
       </c>
       <c r="B475" t="s">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="C475" t="n">
-        <v>11.6749484618605</v>
+        <v>14.5643046518575</v>
       </c>
       <c r="D475" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" s="1" t="n">
-        <v>43800</v>
+        <v>42339</v>
       </c>
       <c r="B476" t="s">
-        <v>51</v>
+        <v>14</v>
       </c>
       <c r="C476" t="n">
-        <v>11.6377705135102</v>
+        <v>14.5588421401419</v>
       </c>
       <c r="D476" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" s="1" t="n">
-        <v>43435</v>
+        <v>42339</v>
       </c>
       <c r="B477" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C477" t="n">
-        <v>11.6298938064506</v>
+        <v>14.5377256710888</v>
       </c>
       <c r="D477" t="n">
-        <v>43</v>
+        <v>33</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" s="1" t="n">
-        <v>44531</v>
+        <v>45992</v>
       </c>
       <c r="B478" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="C478" t="n">
-        <v>11.4540392499305</v>
+        <v>14.5179498837108</v>
       </c>
       <c r="D478" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" s="1" t="n">
-        <v>43070</v>
+        <v>43800</v>
       </c>
       <c r="B479" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="C479" t="n">
-        <v>11.4455961334695</v>
+        <v>14.4990334373857</v>
       </c>
       <c r="D479" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" s="1" t="n">
-        <v>44896</v>
+        <v>42339</v>
       </c>
       <c r="B480" t="s">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="C480" t="n">
-        <v>11.4272244655339</v>
+        <v>14.4913183023972</v>
       </c>
       <c r="D480" t="n">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" s="1" t="n">
-        <v>43435</v>
+        <v>42339</v>
       </c>
       <c r="B481" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C481" t="n">
-        <v>11.268903188306</v>
+        <v>14.4066991150885</v>
       </c>
       <c r="D481" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B482" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="C482" t="n">
-        <v>11.2233710355464</v>
+        <v>14.4030437323642</v>
       </c>
       <c r="D482" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" s="1" t="n">
-        <v>42705</v>
+        <v>44166</v>
       </c>
       <c r="B483" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C483" t="n">
-        <v>11.1896672186228</v>
+        <v>14.3923372618686</v>
       </c>
       <c r="D483" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" s="1" t="n">
-        <v>44531</v>
+        <v>43070</v>
       </c>
       <c r="B484" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C484" t="n">
-        <v>11.1710086703425</v>
+        <v>14.2674094628876</v>
       </c>
       <c r="D484" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" s="1" t="n">
-        <v>43070</v>
+        <v>43435</v>
       </c>
       <c r="B485" t="s">
-        <v>42</v>
+        <v>12</v>
       </c>
       <c r="C485" t="n">
-        <v>11.0885557678522</v>
+        <v>14.2672542057827</v>
       </c>
       <c r="D485" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="B486" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C486" t="n">
-        <v>11.0159991187201</v>
+        <v>14.2202861052197</v>
       </c>
       <c r="D486" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="487">
@@ -7315,55 +7315,55 @@
         <v>43070</v>
       </c>
       <c r="B487" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C487" t="n">
-        <v>11.0159991187201</v>
+        <v>14.1369366888101</v>
       </c>
       <c r="D487" t="n">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="B488" t="s">
         <v>53</v>
       </c>
       <c r="C488" t="n">
-        <v>11.009439808247</v>
+        <v>14.0606274122469</v>
       </c>
       <c r="D488" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" s="1" t="n">
-        <v>43070</v>
+        <v>43435</v>
       </c>
       <c r="B489" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="C489" t="n">
-        <v>10.9464200568101</v>
+        <v>13.9245997875117</v>
       </c>
       <c r="D489" t="n">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" s="1" t="n">
-        <v>43435</v>
+        <v>43070</v>
       </c>
       <c r="B490" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C490" t="n">
-        <v>10.8536537851422</v>
+        <v>13.8975079429074</v>
       </c>
       <c r="D490" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
     </row>
     <row r="491">
@@ -7371,164 +7371,162 @@
         <v>43800</v>
       </c>
       <c r="B491" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="C491" t="n">
-        <v>10.8202381484871</v>
+        <v>13.8965504106184</v>
       </c>
       <c r="D491" t="n">
-        <v>50</v>
+        <v>41</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" s="1" t="n">
-        <v>44166</v>
+        <v>42339</v>
       </c>
       <c r="B492" t="s">
-        <v>55</v>
+        <v>33</v>
       </c>
       <c r="C492" t="n">
-        <v>10.7610633980364</v>
+        <v>13.7262490774802</v>
       </c>
       <c r="D492" t="n">
-        <v>51</v>
+        <v>36</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" s="1" t="n">
-        <v>43070</v>
+        <v>42705</v>
       </c>
       <c r="B493" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="C493" t="n">
-        <v>10.7263399274635</v>
+        <v>13.6911093100919</v>
       </c>
       <c r="D493" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" s="1" t="n">
-        <v>42705</v>
-      </c>
-      <c r="B494" t="s">
-        <v>41</v>
-      </c>
+        <v>45992</v>
+      </c>
+      <c r="B494"/>
       <c r="C494" t="n">
-        <v>10.6749465144253</v>
+        <v>13.6503351882085</v>
       </c>
       <c r="D494" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" s="1" t="n">
-        <v>43435</v>
+        <v>45627</v>
       </c>
       <c r="B495" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C495" t="n">
-        <v>10.5785055172976</v>
+        <v>13.4315165660614</v>
       </c>
       <c r="D495" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" s="1" t="n">
-        <v>42705</v>
+        <v>43435</v>
       </c>
       <c r="B496" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C496" t="n">
-        <v>10.5753549701385</v>
+        <v>13.4134312053817</v>
       </c>
       <c r="D496" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="B497" t="s">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="C497" t="n">
-        <v>10.4400480242209</v>
+        <v>13.2155124445679</v>
       </c>
       <c r="D497" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" s="1" t="n">
-        <v>42705</v>
+        <v>44166</v>
       </c>
       <c r="B498" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C498" t="n">
-        <v>10.3446849008979</v>
+        <v>13.1798722275871</v>
       </c>
       <c r="D498" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" s="1" t="n">
-        <v>43435</v>
+        <v>43800</v>
       </c>
       <c r="B499" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="C499" t="n">
-        <v>10.2936047195502</v>
+        <v>12.9686611080864</v>
       </c>
       <c r="D499" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" s="1" t="n">
-        <v>43070</v>
+        <v>43800</v>
       </c>
       <c r="B500" t="s">
-        <v>50</v>
+        <v>41</v>
       </c>
       <c r="C500" t="n">
-        <v>10.2208461537102</v>
+        <v>12.9599989632001</v>
       </c>
       <c r="D500" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" s="1" t="n">
-        <v>45627</v>
+        <v>43435</v>
       </c>
       <c r="B501" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C501" t="n">
-        <v>10.0931632994437</v>
+        <v>12.9404274481995</v>
       </c>
       <c r="D501" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="B502" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="C502" t="n">
-        <v>9.97975697023651</v>
+        <v>12.9394549928168</v>
       </c>
       <c r="D502" t="n">
         <v>51</v>
@@ -7536,44 +7534,44 @@
     </row>
     <row r="503">
       <c r="A503" s="1" t="n">
-        <v>42705</v>
+        <v>43070</v>
       </c>
       <c r="B503" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="C503" t="n">
-        <v>9.87704028511303</v>
+        <v>12.9166374570342</v>
       </c>
       <c r="D503" t="n">
-        <v>49</v>
+        <v>40</v>
       </c>
     </row>
     <row r="504">
       <c r="A504" s="1" t="n">
-        <v>43070</v>
+        <v>43800</v>
       </c>
       <c r="B504" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C504" t="n">
-        <v>9.82745065585302</v>
+        <v>12.8945117618356</v>
       </c>
       <c r="D504" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="505">
       <c r="A505" s="1" t="n">
-        <v>43435</v>
+        <v>42705</v>
       </c>
       <c r="B505" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C505" t="n">
-        <v>9.77410690783321</v>
+        <v>12.8933713483878</v>
       </c>
       <c r="D505" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
     </row>
     <row r="506">
@@ -7581,108 +7579,108 @@
         <v>42705</v>
       </c>
       <c r="B506" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C506" t="n">
-        <v>9.74271843533328</v>
+        <v>12.839664851484</v>
       </c>
       <c r="D506" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
     </row>
     <row r="507">
       <c r="A507" s="1" t="n">
-        <v>44896</v>
+        <v>43070</v>
       </c>
       <c r="B507" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C507" t="n">
-        <v>9.52613165340758</v>
+        <v>12.8384374351906</v>
       </c>
       <c r="D507" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" s="1" t="n">
-        <v>45261</v>
+        <v>43070</v>
       </c>
       <c r="B508" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C508" t="n">
-        <v>9.52613165340758</v>
+        <v>12.7435179708061</v>
       </c>
       <c r="D508" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" s="1" t="n">
-        <v>42339</v>
+        <v>43070</v>
       </c>
       <c r="B509" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="C509" t="n">
-        <v>9.43666269278316</v>
+        <v>12.6925964845311</v>
       </c>
       <c r="D509" t="n">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" s="1" t="n">
-        <v>43435</v>
+        <v>42339</v>
       </c>
       <c r="B510" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C510" t="n">
-        <v>9.05159928828568</v>
+        <v>12.6733479492627</v>
       </c>
       <c r="D510" t="n">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" s="1" t="n">
-        <v>42339</v>
+        <v>42705</v>
       </c>
       <c r="B511" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C511" t="n">
-        <v>8.93544482387074</v>
+        <v>12.5854416248026</v>
       </c>
       <c r="D511" t="n">
-        <v>49</v>
+        <v>41</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" s="1" t="n">
-        <v>45261</v>
+        <v>43800</v>
       </c>
       <c r="B512" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C512" t="n">
-        <v>8.7625801955439</v>
+        <v>12.4861048728758</v>
       </c>
       <c r="D512" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="513">
       <c r="A513" s="1" t="n">
-        <v>43435</v>
+        <v>45992</v>
       </c>
       <c r="B513" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="C513" t="n">
-        <v>8.71318521966978</v>
+        <v>12.3407141448201</v>
       </c>
       <c r="D513" t="n">
         <v>50</v>
@@ -7693,55 +7691,55 @@
         <v>42339</v>
       </c>
       <c r="B514" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="C514" t="n">
-        <v>8.53436504324078</v>
+        <v>12.3098757107236</v>
       </c>
       <c r="D514" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" s="1" t="n">
-        <v>43070</v>
+        <v>43800</v>
       </c>
       <c r="B515" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="C515" t="n">
-        <v>8.50547469054248</v>
+        <v>12.3018931771004</v>
       </c>
       <c r="D515" t="n">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" s="1" t="n">
-        <v>44166</v>
+        <v>42339</v>
       </c>
       <c r="B516" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C516" t="n">
-        <v>8.39206836133525</v>
+        <v>12.1523815884925</v>
       </c>
       <c r="D516" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" s="1" t="n">
-        <v>43070</v>
+        <v>42339</v>
       </c>
       <c r="B517" t="s">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="C517" t="n">
-        <v>8.04517596900814</v>
+        <v>12.0693382213562</v>
       </c>
       <c r="D517" t="n">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="518">
@@ -7749,13 +7747,13 @@
         <v>42705</v>
       </c>
       <c r="B518" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="C518" t="n">
-        <v>7.82503671529908</v>
+        <v>12.0515966490022</v>
       </c>
       <c r="D518" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="519">
@@ -7763,168 +7761,910 @@
         <v>43800</v>
       </c>
       <c r="B519" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C519" t="n">
-        <v>7.48150121958719</v>
+        <v>12.0413437208218</v>
       </c>
       <c r="D519" t="n">
-        <v>52</v>
+        <v>47</v>
       </c>
     </row>
     <row r="520">
       <c r="A520" s="1" t="n">
-        <v>45627</v>
+        <v>42339</v>
       </c>
       <c r="B520" t="s">
-        <v>55</v>
+        <v>18</v>
       </c>
       <c r="C520" t="n">
-        <v>7.43025806054892</v>
+        <v>11.8131469153782</v>
       </c>
       <c r="D520" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="521">
       <c r="A521" s="1" t="n">
-        <v>43435</v>
+        <v>42339</v>
       </c>
       <c r="B521" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C521" t="n">
-        <v>7.17404226535758</v>
+        <v>11.8126513495954</v>
       </c>
       <c r="D521" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="522">
       <c r="A522" s="1" t="n">
-        <v>42339</v>
+        <v>42705</v>
       </c>
       <c r="B522" t="s">
-        <v>54</v>
+        <v>18</v>
       </c>
       <c r="C522" t="n">
-        <v>7.03119241084845</v>
+        <v>11.7893780081038</v>
       </c>
       <c r="D522" t="n">
-        <v>51</v>
+        <v>43</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" s="1" t="n">
-        <v>43435</v>
+        <v>42339</v>
       </c>
       <c r="B523" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
       <c r="C523" t="n">
-        <v>6.46416076481228</v>
+        <v>11.764722070481</v>
       </c>
       <c r="D523" t="n">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" s="1" t="n">
-        <v>42339</v>
+        <v>42705</v>
       </c>
       <c r="B524" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="C524" t="n">
-        <v>6.30290856170701</v>
+        <v>11.7097835947343</v>
       </c>
       <c r="D524" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" s="1" t="n">
-        <v>42705</v>
+        <v>42339</v>
       </c>
       <c r="B525" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
       <c r="C525" t="n">
-        <v>5.79047697132433</v>
+        <v>11.6749484618605</v>
       </c>
       <c r="D525" t="n">
-        <v>52</v>
+        <v>44</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" s="1" t="n">
-        <v>43800</v>
-      </c>
-      <c r="B526"/>
+        <v>45992</v>
+      </c>
+      <c r="B526" t="s">
+        <v>53</v>
+      </c>
       <c r="C526" t="n">
-        <v>5.28497490693914</v>
+        <v>11.6700061967418</v>
       </c>
       <c r="D526" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" s="1" t="n">
-        <v>44166</v>
-      </c>
-      <c r="B527"/>
+        <v>43800</v>
+      </c>
+      <c r="B527" t="s">
+        <v>51</v>
+      </c>
       <c r="C527" t="n">
-        <v>4.71117763132861</v>
+        <v>11.6377705135102</v>
       </c>
       <c r="D527" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" s="1" t="n">
-        <v>43070</v>
-      </c>
-      <c r="B528"/>
+        <v>43435</v>
+      </c>
+      <c r="B528" t="s">
+        <v>41</v>
+      </c>
       <c r="C528" t="n">
-        <v>1.90259096649809</v>
+        <v>11.6298938064506</v>
       </c>
       <c r="D528" t="n">
-        <v>53</v>
+        <v>43</v>
       </c>
     </row>
     <row r="529">
       <c r="A529" s="1" t="n">
-        <v>43435</v>
-      </c>
-      <c r="B529"/>
+        <v>44531</v>
+      </c>
+      <c r="B529" t="s">
+        <v>54</v>
+      </c>
       <c r="C529" t="n">
-        <v>1.90259096649809</v>
+        <v>11.4540392499305</v>
       </c>
       <c r="D529" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" s="1" t="n">
-        <v>42705</v>
-      </c>
-      <c r="B530"/>
+        <v>43070</v>
+      </c>
+      <c r="B530" t="s">
+        <v>46</v>
+      </c>
       <c r="C530" t="n">
-        <v>1.47979297394296</v>
+        <v>11.4455961334695</v>
       </c>
       <c r="D530" t="n">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B531" t="s">
+        <v>55</v>
+      </c>
+      <c r="C531" t="n">
+        <v>11.4272244655339</v>
+      </c>
+      <c r="D531" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B532" t="s">
+        <v>44</v>
+      </c>
+      <c r="C532" t="n">
+        <v>11.268903188306</v>
+      </c>
+      <c r="D532" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="n">
         <v>42339</v>
       </c>
-      <c r="B531"/>
-      <c r="C531" t="n">
+      <c r="B533" t="s">
+        <v>42</v>
+      </c>
+      <c r="C533" t="n">
+        <v>11.2233710355464</v>
+      </c>
+      <c r="D533" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B534" t="s">
+        <v>42</v>
+      </c>
+      <c r="C534" t="n">
+        <v>11.1896672186228</v>
+      </c>
+      <c r="D534" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="n">
+        <v>44531</v>
+      </c>
+      <c r="B535" t="s">
+        <v>55</v>
+      </c>
+      <c r="C535" t="n">
+        <v>11.1710086703425</v>
+      </c>
+      <c r="D535" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B536" t="s">
+        <v>42</v>
+      </c>
+      <c r="C536" t="n">
+        <v>11.0885557678522</v>
+      </c>
+      <c r="D536" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="B537" t="s">
+        <v>41</v>
+      </c>
+      <c r="C537" t="n">
+        <v>11.0159991187201</v>
+      </c>
+      <c r="D537" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B538" t="s">
+        <v>41</v>
+      </c>
+      <c r="C538" t="n">
+        <v>11.0159991187201</v>
+      </c>
+      <c r="D538" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="n">
+        <v>43800</v>
+      </c>
+      <c r="B539" t="s">
+        <v>53</v>
+      </c>
+      <c r="C539" t="n">
+        <v>11.009439808247</v>
+      </c>
+      <c r="D539" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B540" t="s">
+        <v>52</v>
+      </c>
+      <c r="C540" t="n">
+        <v>10.9464200568101</v>
+      </c>
+      <c r="D540" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B541" t="s">
+        <v>52</v>
+      </c>
+      <c r="C541" t="n">
+        <v>10.8536537851422</v>
+      </c>
+      <c r="D541" t="n">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="n">
+        <v>43800</v>
+      </c>
+      <c r="B542" t="s">
+        <v>50</v>
+      </c>
+      <c r="C542" t="n">
+        <v>10.8202381484871</v>
+      </c>
+      <c r="D542" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B543" t="s">
+        <v>55</v>
+      </c>
+      <c r="C543" t="n">
+        <v>10.7610633980364</v>
+      </c>
+      <c r="D543" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B544" t="s">
+        <v>53</v>
+      </c>
+      <c r="C544" t="n">
+        <v>10.7263399274635</v>
+      </c>
+      <c r="D544" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B545" t="s">
+        <v>41</v>
+      </c>
+      <c r="C545" t="n">
+        <v>10.6749465144253</v>
+      </c>
+      <c r="D545" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B546" t="s">
+        <v>46</v>
+      </c>
+      <c r="C546" t="n">
+        <v>10.5785055172976</v>
+      </c>
+      <c r="D546" t="n">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B547" t="s">
+        <v>52</v>
+      </c>
+      <c r="C547" t="n">
+        <v>10.5753549701385</v>
+      </c>
+      <c r="D547" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="B548" t="s">
+        <v>44</v>
+      </c>
+      <c r="C548" t="n">
+        <v>10.4400480242209</v>
+      </c>
+      <c r="D548" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B549" t="s">
+        <v>51</v>
+      </c>
+      <c r="C549" t="n">
+        <v>10.3446849008979</v>
+      </c>
+      <c r="D549" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B550" t="s">
+        <v>54</v>
+      </c>
+      <c r="C550" t="n">
+        <v>10.3199759578582</v>
+      </c>
+      <c r="D550" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B551" t="s">
+        <v>50</v>
+      </c>
+      <c r="C551" t="n">
+        <v>10.2936047195502</v>
+      </c>
+      <c r="D551" t="n">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B552" t="s">
+        <v>50</v>
+      </c>
+      <c r="C552" t="n">
+        <v>10.2208461537102</v>
+      </c>
+      <c r="D552" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B553" t="s">
+        <v>54</v>
+      </c>
+      <c r="C553" t="n">
+        <v>10.0931632994437</v>
+      </c>
+      <c r="D553" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="n">
+        <v>43800</v>
+      </c>
+      <c r="B554" t="s">
+        <v>54</v>
+      </c>
+      <c r="C554" t="n">
+        <v>9.97975697023651</v>
+      </c>
+      <c r="D554" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B555" t="s">
+        <v>53</v>
+      </c>
+      <c r="C555" t="n">
+        <v>9.87704028511303</v>
+      </c>
+      <c r="D555" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B556" t="s">
+        <v>51</v>
+      </c>
+      <c r="C556" t="n">
+        <v>9.82745065585302</v>
+      </c>
+      <c r="D556" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B557" t="s">
+        <v>42</v>
+      </c>
+      <c r="C557" t="n">
+        <v>9.77410690783321</v>
+      </c>
+      <c r="D557" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B558" t="s">
+        <v>50</v>
+      </c>
+      <c r="C558" t="n">
+        <v>9.74271843533328</v>
+      </c>
+      <c r="D558" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="n">
+        <v>44896</v>
+      </c>
+      <c r="B559" t="s">
+        <v>54</v>
+      </c>
+      <c r="C559" t="n">
+        <v>9.52613165340758</v>
+      </c>
+      <c r="D559" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B560" t="s">
+        <v>54</v>
+      </c>
+      <c r="C560" t="n">
+        <v>9.52613165340758</v>
+      </c>
+      <c r="D560" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="B561" t="s">
+        <v>53</v>
+      </c>
+      <c r="C561" t="n">
+        <v>9.43666269278316</v>
+      </c>
+      <c r="D561" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B562" t="s">
+        <v>51</v>
+      </c>
+      <c r="C562" t="n">
+        <v>9.05159928828568</v>
+      </c>
+      <c r="D562" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="B563" t="s">
+        <v>50</v>
+      </c>
+      <c r="C563" t="n">
+        <v>8.93544482387074</v>
+      </c>
+      <c r="D563" t="n">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="n">
+        <v>45261</v>
+      </c>
+      <c r="B564" t="s">
+        <v>55</v>
+      </c>
+      <c r="C564" t="n">
+        <v>8.7625801955439</v>
+      </c>
+      <c r="D564" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B565" t="s">
+        <v>53</v>
+      </c>
+      <c r="C565" t="n">
+        <v>8.71318521966978</v>
+      </c>
+      <c r="D565" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="B566" t="s">
+        <v>51</v>
+      </c>
+      <c r="C566" t="n">
+        <v>8.53436504324078</v>
+      </c>
+      <c r="D566" t="n">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B567" t="s">
+        <v>54</v>
+      </c>
+      <c r="C567" t="n">
+        <v>8.50547469054248</v>
+      </c>
+      <c r="D567" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B568" t="s">
+        <v>54</v>
+      </c>
+      <c r="C568" t="n">
+        <v>8.39206836133525</v>
+      </c>
+      <c r="D568" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B569" t="s">
+        <v>55</v>
+      </c>
+      <c r="C569" t="n">
+        <v>8.04517596900814</v>
+      </c>
+      <c r="D569" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B570" t="s">
+        <v>54</v>
+      </c>
+      <c r="C570" t="n">
+        <v>7.82503671529908</v>
+      </c>
+      <c r="D570" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="n">
+        <v>43800</v>
+      </c>
+      <c r="B571" t="s">
+        <v>55</v>
+      </c>
+      <c r="C571" t="n">
+        <v>7.48150121958719</v>
+      </c>
+      <c r="D571" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="n">
+        <v>45627</v>
+      </c>
+      <c r="B572" t="s">
+        <v>55</v>
+      </c>
+      <c r="C572" t="n">
+        <v>7.43025806054892</v>
+      </c>
+      <c r="D572" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B573" t="s">
+        <v>55</v>
+      </c>
+      <c r="C573" t="n">
+        <v>7.43025806054892</v>
+      </c>
+      <c r="D573" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B574" t="s">
+        <v>55</v>
+      </c>
+      <c r="C574" t="n">
+        <v>7.17404226535758</v>
+      </c>
+      <c r="D574" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="B575" t="s">
+        <v>54</v>
+      </c>
+      <c r="C575" t="n">
+        <v>7.03119241084845</v>
+      </c>
+      <c r="D575" t="n">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B576" t="s">
+        <v>54</v>
+      </c>
+      <c r="C576" t="n">
+        <v>6.46416076481228</v>
+      </c>
+      <c r="D576" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="B577" t="s">
+        <v>55</v>
+      </c>
+      <c r="C577" t="n">
+        <v>6.30290856170701</v>
+      </c>
+      <c r="D577" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B578" t="s">
+        <v>55</v>
+      </c>
+      <c r="C578" t="n">
+        <v>5.79047697132433</v>
+      </c>
+      <c r="D578" t="n">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>43800</v>
+      </c>
+      <c r="B579"/>
+      <c r="C579" t="n">
+        <v>5.28497490693914</v>
+      </c>
+      <c r="D579" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>44166</v>
+      </c>
+      <c r="B580"/>
+      <c r="C580" t="n">
+        <v>4.71117763132861</v>
+      </c>
+      <c r="D580" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>43070</v>
+      </c>
+      <c r="B581"/>
+      <c r="C581" t="n">
+        <v>1.90259096649809</v>
+      </c>
+      <c r="D581" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="B582"/>
+      <c r="C582" t="n">
+        <v>1.90259096649809</v>
+      </c>
+      <c r="D582" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="B583"/>
+      <c r="C583" t="n">
+        <v>1.47979297394296</v>
+      </c>
+      <c r="D583" t="n">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="B584"/>
+      <c r="C584" t="n">
         <v>0.966395411554586</v>
       </c>
-      <c r="D531" t="n">
+      <c r="D584" t="n">
         <v>53</v>
       </c>
     </row>
